--- a/docs/compliance/ICS_DMAS_master_capability_matrix.xlsx
+++ b/docs/compliance/ICS_DMAS_master_capability_matrix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd2d3534488626a3/文件/民防/研究資料/! [研究] ICS_DMAS_docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yello\研究計畫\ICS_DMAS\docs\compliance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_FF57A87D6457DD570D45840AA31CCED1EFE1B979" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E5C41CC-025B-422A-99C6-0C14335D7F1B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CF6AFC-5703-4BF1-9938-27C67464CD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="565">
   <si>
     <t>ICS_DMAS Master Capability Matrix</t>
   </si>
@@ -692,9 +692,6 @@
   </si>
   <si>
     <t>不建議外部宣稱細節</t>
-  </si>
-  <si>
-    <t>Needs Hotfix</t>
   </si>
   <si>
     <t>列為 HOTFIX-WS-01</t>
@@ -1853,12 +1850,37 @@
     </r>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
+  <si>
+    <t>Last Update</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>Needs Hotfix</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; Partial Hardened</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1946,6 +1968,11 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1956,7 +1983,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1983,7 +2010,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -1991,10 +2018,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2011,6 +2034,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -2055,8 +2084,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CapabilityMatrix" displayName="CapabilityMatrix" ref="A4:T38">
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="CapabilityMatrix" displayName="CapabilityMatrix" ref="A4:U38">
+  <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Capability ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Capability"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Capability Group"/>
@@ -2077,6 +2106,7 @@
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="Owner"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0200-000013000000}" name="Priority"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0200-000014000000}" name="Disclosure"/>
+    <tableColumn id="21" xr3:uid="{AFEB0359-48C2-466B-8D9A-13AD724F7F93}" name="Last Update"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2289,18 +2319,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
@@ -2319,18 +2349,18 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2455,11 +2485,12 @@
     <col min="13" max="13" width="22" customWidth="1"/>
     <col min="14" max="14" width="45" customWidth="1"/>
     <col min="15" max="15" width="36" customWidth="1"/>
-    <col min="16" max="16" width="18" style="12" customWidth="1"/>
+    <col min="16" max="16" width="16.77734375" style="8" customWidth="1"/>
     <col min="17" max="17" width="42" customWidth="1"/>
     <col min="18" max="18" width="22" customWidth="1"/>
     <col min="19" max="19" width="10" customWidth="1"/>
     <col min="20" max="20" width="22" customWidth="1"/>
+    <col min="21" max="21" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2480,7 +2511,7 @@
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
-      <c r="P1" s="11"/>
+      <c r="P1" s="7"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
@@ -2543,7 +2574,7 @@
       <c r="O4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="9" t="s">
         <v>38</v>
       </c>
       <c r="Q4" s="1" t="s">
@@ -2557,6 +2588,9 @@
       </c>
       <c r="T4" s="1" t="s">
         <v>42</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -2605,7 +2639,7 @@
       <c r="O5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P5" s="14" t="s">
+      <c r="P5" s="10" t="s">
         <v>58</v>
       </c>
       <c r="Q5" s="3" t="s">
@@ -2667,7 +2701,7 @@
       <c r="O6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="P6" s="14" t="s">
+      <c r="P6" s="10" t="s">
         <v>58</v>
       </c>
       <c r="Q6" s="3" t="s">
@@ -2729,7 +2763,7 @@
       <c r="O7" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="P7" s="10" t="s">
         <v>58</v>
       </c>
       <c r="Q7" s="3" t="s">
@@ -2791,7 +2825,7 @@
       <c r="O8" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="P8" s="14" t="s">
+      <c r="P8" s="10" t="s">
         <v>58</v>
       </c>
       <c r="Q8" s="3" t="s">
@@ -2853,7 +2887,7 @@
       <c r="O9" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="P9" s="10" t="s">
         <v>58</v>
       </c>
       <c r="Q9" s="3" t="s">
@@ -2915,7 +2949,7 @@
       <c r="O10" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="P10" s="14" t="s">
+      <c r="P10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="Q10" s="3" t="s">
@@ -2977,7 +3011,7 @@
       <c r="O11" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="P11" s="14" t="s">
+      <c r="P11" s="10" t="s">
         <v>17</v>
       </c>
       <c r="Q11" s="3" t="s">
@@ -3039,7 +3073,7 @@
       <c r="O12" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="P12" s="14" t="s">
+      <c r="P12" s="10" t="s">
         <v>58</v>
       </c>
       <c r="Q12" s="3" t="s">
@@ -3101,7 +3135,7 @@
       <c r="O13" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="P13" s="14" t="s">
+      <c r="P13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="Q13" s="3" t="s">
@@ -3118,7 +3152,7 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="19" t="s">
         <v>168</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -3163,11 +3197,11 @@
       <c r="O14" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="P14" s="15" t="s">
+      <c r="P14" s="11" t="s">
+        <v>561</v>
+      </c>
+      <c r="Q14" s="12" t="s">
         <v>562</v>
-      </c>
-      <c r="Q14" s="16" t="s">
-        <v>563</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>180</v>
@@ -3177,6 +3211,9 @@
       </c>
       <c r="T14" s="3" t="s">
         <v>181</v>
+      </c>
+      <c r="U14" s="14">
+        <v>46138</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -3225,7 +3262,7 @@
       <c r="O15" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="P15" s="14" t="s">
+      <c r="P15" s="10" t="s">
         <v>58</v>
       </c>
       <c r="Q15" s="3" t="s">
@@ -3287,7 +3324,7 @@
       <c r="O16" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="P16" s="14" t="s">
+      <c r="P16" s="10" t="s">
         <v>17</v>
       </c>
       <c r="Q16" s="3" t="s">
@@ -3303,8 +3340,8 @@
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
         <v>207</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -3349,14 +3386,14 @@
       <c r="O17" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="P17" s="14" t="s">
+      <c r="P17" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q17" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="Q17" s="3" t="s">
+      <c r="R17" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>219</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>77</v>
@@ -3364,25 +3401,28 @@
       <c r="T17" s="3" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="U17" s="14">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>49</v>
@@ -3391,34 +3431,34 @@
         <v>67</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>124</v>
       </c>
       <c r="K18" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>164</v>
       </c>
       <c r="N18" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="O18" s="3" t="s">
+      <c r="P18" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="P18" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q18" s="3" t="s">
+      <c r="R18" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>61</v>
@@ -3427,24 +3467,24 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>49</v>
@@ -3453,34 +3493,34 @@
         <v>67</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>124</v>
       </c>
       <c r="K19" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>164</v>
       </c>
       <c r="N19" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="O19" s="3" t="s">
+      <c r="P19" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="P19" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="R19" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>61</v>
@@ -3489,24 +3529,24 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>49</v>
@@ -3515,34 +3555,34 @@
         <v>67</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>69</v>
       </c>
       <c r="K20" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>253</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>112</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="P20" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q20" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="P20" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q20" s="3" t="s">
+      <c r="R20" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>61</v>
@@ -3551,24 +3591,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>122</v>
@@ -3577,34 +3617,34 @@
         <v>50</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>69</v>
       </c>
       <c r="K21" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>85</v>
       </c>
       <c r="N21" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q21" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="P21" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>267</v>
-      </c>
       <c r="R21" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>141</v>
@@ -3613,24 +3653,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>49</v>
@@ -3639,54 +3679,54 @@
         <v>67</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>69</v>
       </c>
       <c r="K22" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="P22" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q22" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="P22" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q22" s="3" t="s">
+      <c r="R22" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>61</v>
       </c>
       <c r="T22" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>286</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>94</v>
@@ -3701,13 +3741,13 @@
         <v>50</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>52</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>137</v>
@@ -3716,16 +3756,16 @@
         <v>85</v>
       </c>
       <c r="N23" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="O23" s="3" t="s">
+      <c r="P23" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q23" s="3" t="s">
         <v>290</v>
-      </c>
-      <c r="P23" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>291</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>89</v>
@@ -3737,24 +3777,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>122</v>
@@ -3763,31 +3803,31 @@
         <v>67</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>124</v>
       </c>
       <c r="K24" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>112</v>
       </c>
       <c r="N24" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="O24" s="3" t="s">
+      <c r="P24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="P24" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>89</v>
@@ -3799,24 +3839,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>122</v>
@@ -3825,60 +3865,60 @@
         <v>67</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>124</v>
       </c>
       <c r="K25" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>112</v>
       </c>
       <c r="N25" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="O25" s="3" t="s">
+      <c r="P25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q25" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="P25" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q25" s="3" t="s">
+      <c r="R25" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="R25" s="3" t="s">
+      <c r="S25" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="S25" s="3" t="s">
+      <c r="T25" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="T25" s="3" t="s">
+    </row>
+    <row r="26" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3" t="s">
+      <c r="B26" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>49</v>
@@ -3887,34 +3927,34 @@
         <v>67</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>124</v>
       </c>
       <c r="K26" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>325</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>85</v>
       </c>
       <c r="N26" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="O26" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="O26" s="3" t="s">
+      <c r="P26" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q26" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="P26" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q26" s="3" t="s">
+      <c r="R26" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>141</v>
@@ -3923,24 +3963,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>335</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>49</v>
@@ -3949,34 +3989,34 @@
         <v>67</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>124</v>
       </c>
       <c r="K27" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="N27" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="N27" s="3" t="s">
+      <c r="O27" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="O27" s="3" t="s">
+      <c r="P27" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q27" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="P27" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q27" s="3" t="s">
+      <c r="R27" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>61</v>
@@ -3985,24 +4025,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>348</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>349</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>49</v>
@@ -4011,34 +4051,34 @@
         <v>67</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>124</v>
       </c>
       <c r="K28" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>85</v>
       </c>
       <c r="N28" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="O28" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="O28" s="3" t="s">
+      <c r="P28" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q28" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="P28" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q28" s="3" t="s">
+      <c r="R28" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>356</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>61</v>
@@ -4047,24 +4087,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>122</v>
@@ -4073,34 +4113,34 @@
         <v>67</v>
       </c>
       <c r="I29" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="N29" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="N29" s="3" t="s">
+      <c r="O29" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="P29" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q29" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="P29" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q29" s="3" t="s">
+      <c r="R29" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>369</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>77</v>
@@ -4109,24 +4149,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>49</v>
@@ -4135,34 +4175,34 @@
         <v>67</v>
       </c>
       <c r="I30" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K30" s="3" t="s">
+      <c r="L30" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L30" s="3" t="s">
+      <c r="M30" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="N30" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="M30" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="N30" s="3" t="s">
+      <c r="O30" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="O30" s="3" t="s">
+      <c r="P30" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q30" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="P30" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q30" s="3" t="s">
+      <c r="R30" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>380</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>77</v>
@@ -4171,24 +4211,24 @@
         <v>181</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>386</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>122</v>
@@ -4197,34 +4237,34 @@
         <v>67</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>174</v>
       </c>
       <c r="K31" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>164</v>
       </c>
       <c r="N31" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="O31" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="O31" s="3" t="s">
+      <c r="P31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q31" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="P31" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q31" s="3" t="s">
+      <c r="R31" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>61</v>
@@ -4233,24 +4273,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>396</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>397</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>121</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>122</v>
@@ -4259,60 +4299,60 @@
         <v>50</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>112</v>
       </c>
       <c r="N32" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="O32" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="O32" s="3" t="s">
+      <c r="P32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q32" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="P32" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q32" s="3" t="s">
+      <c r="R32" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>406</v>
-      </c>
       <c r="S32" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="T32" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>122</v>
@@ -4321,60 +4361,60 @@
         <v>50</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="K33" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="L33" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>85</v>
       </c>
       <c r="N33" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="O33" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="O33" s="3" t="s">
+      <c r="P33" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q33" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="P33" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>418</v>
-      </c>
       <c r="R33" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="S33" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="T33" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>423</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>122</v>
@@ -4383,60 +4423,60 @@
         <v>50</v>
       </c>
       <c r="I34" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="J34" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="K34" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="L34" s="3" t="s">
+      <c r="M34" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="N34" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="N34" s="3" t="s">
+      <c r="O34" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="O34" s="3" t="s">
+      <c r="P34" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q34" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="P34" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q34" s="3" t="s">
+      <c r="R34" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="R34" s="3" t="s">
+      <c r="S34" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="S34" s="3" t="s">
+      <c r="T34" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>439</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>440</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>122</v>
@@ -4445,34 +4485,34 @@
         <v>67</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>174</v>
       </c>
       <c r="K35" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>164</v>
       </c>
       <c r="N35" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="O35" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="O35" s="3" t="s">
+      <c r="P35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q35" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="P35" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q35" s="3" t="s">
+      <c r="R35" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>141</v>
@@ -4483,22 +4523,22 @@
     </row>
     <row r="36" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>122</v>
@@ -4507,37 +4547,37 @@
         <v>67</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="K36" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="L36" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="L36" s="3" t="s">
+      <c r="M36" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="N36" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="M36" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="N36" s="3" t="s">
+      <c r="O36" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="O36" s="3" t="s">
+      <c r="P36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q36" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="P36" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q36" s="3" t="s">
+      <c r="R36" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="R36" s="3" t="s">
-        <v>460</v>
-      </c>
       <c r="S36" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="T36" s="3" t="s">
         <v>62</v>
@@ -4545,22 +4585,22 @@
     </row>
     <row r="37" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>146</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>122</v>
@@ -4569,60 +4609,60 @@
         <v>50</v>
       </c>
       <c r="I37" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="J37" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="K37" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="K37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="L37" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="M37" s="3" t="s">
+      <c r="N37" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="N37" s="3" t="s">
+      <c r="O37" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="O37" s="3" t="s">
+      <c r="P37" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q37" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="P37" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q37" s="3" t="s">
+      <c r="R37" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="R37" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>141</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>479</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>122</v>
@@ -4631,34 +4671,34 @@
         <v>67</v>
       </c>
       <c r="I38" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="K38" s="3" t="s">
+      <c r="L38" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L38" s="3" t="s">
+      <c r="M38" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="N38" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="N38" s="3" t="s">
+      <c r="O38" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="O38" s="3" t="s">
+      <c r="P38" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q38" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="P38" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q38" s="3" t="s">
+      <c r="R38" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="R38" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="S38" s="3" t="s">
         <v>61</v>
@@ -4688,12 +4728,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
@@ -4718,25 +4758,25 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="4" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4744,13 +4784,13 @@
         <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4758,10 +4798,10 @@
         <v>94</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>496</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>69</v>
@@ -4772,41 +4812,41 @@
         <v>186</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>501</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -4834,12 +4874,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="A1" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
@@ -4864,25 +4904,25 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="4" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4890,13 +4930,13 @@
         <v>122</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4904,13 +4944,13 @@
         <v>49</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4918,13 +4958,13 @@
         <v>50</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>518</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4932,27 +4972,27 @@
         <v>67</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -4980,12 +5020,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="A1" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
@@ -5010,39 +5050,39 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="4" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="57.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>535</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="57.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -5050,10 +5090,10 @@
         <v>52</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>62</v>
@@ -5064,27 +5104,27 @@
         <v>124</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="57.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>542</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -5112,12 +5152,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
+      <c r="A1" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
@@ -5142,12 +5182,12 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="4" spans="1:26" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -5157,7 +5197,7 @@
         <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>40</v>
@@ -5168,7 +5208,7 @@
         <v>64</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>69</v>
@@ -5179,16 +5219,16 @@
     </row>
     <row r="6" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -5196,7 +5236,7 @@
         <v>91</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>52</v>
@@ -5210,21 +5250,21 @@
         <v>143</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>553</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>69</v>
@@ -5235,38 +5275,38 @@
     </row>
     <row r="10" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>555</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>124</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>124</v>
@@ -5277,30 +5317,30 @@
     </row>
     <row r="13" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>124</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="51.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/docs/compliance/ICS_DMAS_master_capability_matrix.xlsx
+++ b/docs/compliance/ICS_DMAS_master_capability_matrix.xlsx
@@ -2,6 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
@@ -10,15 +13,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maturity Definitions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edition Gates" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issue Traceability" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="25">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -26,34 +31,28 @@
     <font>
       <name val="Carlito"/>
       <b val="1"/>
-      <color rgb="001F2937"/>
+      <color rgb="FF1F2937"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Carlito"/>
-      <color rgb="004B5563"/>
+      <color rgb="FF4B5563"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Carlito"/>
       <b val="1"/>
-      <color rgb="001F2937"/>
+      <color rgb="FF1F2937"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Carlito"/>
-      <color rgb="00374151"/>
+      <color rgb="FF374151"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Carlito"/>
-      <color rgb="00111827"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
+      <color rgb="FF111827"/>
       <sz val="10"/>
     </font>
     <font>
@@ -63,30 +62,92 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="001F2937"/>
+      <color rgb="FF1F2937"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Wawati TC"/>
+      <charset val="136"/>
+      <family val="3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="FF4B5563"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="FF111827"/>
       <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F3A5F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
       <sz val="14"/>
     </font>
     <font>
       <i val="1"/>
-      <sz val="10"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
+      <color rgb="001F3A5F"/>
+      <sz val="13"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -95,84 +156,394 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
+        <fgColor rgb="FF2E4057"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8F9FA"/>
+        <fgColor rgb="FFF8F9FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE7F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
-    <border/>
-    <border/>
     <border>
-      <bottom style="thin">
-        <color rgb="00B8CBDD"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00B8CBDD"/>
+        <color rgb="FFB8CBDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <sz val="16"/>
+        <vertAlign val="baseline"/>
+      </font>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -250,7 +621,7 @@
     <tableColumn id="1" name="項目"/>
     <tableColumn id="2" name="內容"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -260,35 +631,36 @@
     <tableColumn id="1" name="KPI"/>
     <tableColumn id="2" name="公式/值"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CapabilityMatrix" displayName="CapabilityMatrix" ref="A4:T38" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CapabilityMatrix" displayName="CapabilityMatrix" ref="A4:T38" headerRowCount="1" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+  <autoFilter ref="A4:T38"/>
   <tableColumns count="20">
-    <tableColumn id="1" name="Capability ID"/>
-    <tableColumn id="2" name="Capability"/>
-    <tableColumn id="3" name="Capability Group"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Golden Path(s)"/>
-    <tableColumn id="6" name="Primary User(s)"/>
-    <tableColumn id="7" name="Current Maturity"/>
-    <tableColumn id="8" name="Target Maturity"/>
-    <tableColumn id="9" name="Acceptance Criteria"/>
-    <tableColumn id="10" name="Edition Gate"/>
-    <tableColumn id="11" name="Security Gate / Dependency"/>
-    <tableColumn id="12" name="Compliance Mapping"/>
-    <tableColumn id="13" name="Data Sensitivity"/>
-    <tableColumn id="14" name="Evidence Required"/>
-    <tableColumn id="15" name="External Claim"/>
-    <tableColumn id="16" name="Status"/>
-    <tableColumn id="17" name="Next Action"/>
-    <tableColumn id="18" name="Owner"/>
-    <tableColumn id="19" name="Priority"/>
-    <tableColumn id="20" name="Disclosure"/>
+    <tableColumn id="1" name="Capability ID" dataDxfId="22"/>
+    <tableColumn id="2" name="Capability" dataDxfId="21"/>
+    <tableColumn id="3" name="Capability Group" dataDxfId="20"/>
+    <tableColumn id="4" name="Description" dataDxfId="19"/>
+    <tableColumn id="5" name="Golden Path(s)" dataDxfId="18"/>
+    <tableColumn id="6" name="Primary User(s)" dataDxfId="17"/>
+    <tableColumn id="7" name="Current Maturity" dataDxfId="16"/>
+    <tableColumn id="8" name="Target Maturity" dataDxfId="15"/>
+    <tableColumn id="9" name="Acceptance Criteria" dataDxfId="14"/>
+    <tableColumn id="10" name="Edition Gate" dataDxfId="13"/>
+    <tableColumn id="11" name="Security Gate / Dependency" dataDxfId="12"/>
+    <tableColumn id="12" name="Compliance Mapping" dataDxfId="11"/>
+    <tableColumn id="13" name="Data Sensitivity" dataDxfId="10"/>
+    <tableColumn id="14" name="Evidence Required" dataDxfId="9"/>
+    <tableColumn id="15" name="External Claim" dataDxfId="8"/>
+    <tableColumn id="16" name="Status" dataDxfId="7"/>
+    <tableColumn id="17" name="Next Action" dataDxfId="6"/>
+    <tableColumn id="18" name="Owner" dataDxfId="5"/>
+    <tableColumn id="19" name="Priority" dataDxfId="4"/>
+    <tableColumn id="20" name="Disclosure" dataDxfId="3"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -300,7 +672,7 @@
     <tableColumn id="3" name="Description"/>
     <tableColumn id="4" name="Primary Use"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -312,7 +684,7 @@
     <tableColumn id="3" name="Definition"/>
     <tableColumn id="4" name="Claim Boundary"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -324,7 +696,7 @@
     <tableColumn id="3" name="Minimum Conditions"/>
     <tableColumn id="4" name="Disclosure / Deliverable Level"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -336,7 +708,7 @@
     <tableColumn id="3" name="Edition / Gate"/>
     <tableColumn id="4" name="Owner"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -482,6 +854,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -491,504 +865,1112 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="6" min="1" max="1"/>
-    <col width="20" customWidth="1" style="6" min="2" max="2"/>
-    <col width="28" customWidth="1" style="6" min="3" max="3"/>
-    <col width="18" customWidth="1" style="6" min="4" max="4"/>
-    <col width="14" customWidth="1" style="6" min="5" max="5"/>
-    <col width="50" customWidth="1" style="6" min="6" max="6"/>
-    <col width="14" customWidth="1" style="6" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>ICS_DMAS Release Dashboard (Tab 1 — Human View)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>受眾：Human owner / 業務 / 投標。技術細節 → Capability Matrix sheet。由 Matrix Steward 每次 Issue 關閉後更新。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>ICS_DMAS — Release Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Audience: Human owner / Business / Procurement  |  Maintained by Matrix Steward after each Issue closes  |  Technical detail → Capability Matrix sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>A.  Release Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Edition</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>GP Scope</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>P0 Issues</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>P1 Issues</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
-        <is>
-          <t>Claims unlocked</t>
-        </is>
-      </c>
-      <c r="G4" s="24" t="inlineStr">
-        <is>
-          <t>Last updated</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>Claims (after Release Acceptance)</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>GP Scope not included</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>v0.12.x</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Demo</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
-        <is>
-          <t>✅ closed</t>
-        </is>
-      </c>
-      <c r="F5" s="25" t="inlineStr">
-        <is>
-          <t>可展示 ICS 基本 COP 流程</t>
-        </is>
-      </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>COP basic demo</t>
+        </is>
+      </c>
+      <c r="H6" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>v0.13.0</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>Demo</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>#6 ✅</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t>🔄 in progress</t>
-        </is>
-      </c>
-      <c r="F6" s="26" t="inlineStr">
-        <is>
-          <t>Pi 部署需 IT 人員一次性 token；fresh DB 不含預設帳號</t>
-        </is>
-      </c>
-      <c r="G6" s="26" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>#6 CLOSED</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>Pi first-run secure deploy</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>TTX, AAR, RBAC, encryption</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>v2.1.0</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>Exercise Pro</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>GP2 + GP3</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>#6✅ #8✅ #11🔄 + TBD</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
-        <is>
-          <t>🔄 building</t>
-        </is>
-      </c>
-      <c r="F7" s="26" t="inlineStr">
-        <is>
-          <t>NIST 800-53 Moderate (scoped) · 個資法§27 · 附表十 12項 · 可投標縣市政府演訓採購</t>
-        </is>
-      </c>
-      <c r="G7" s="26" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>BUILDING</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>Field drill support | GP2+GP3 closed | NIST 800-53 scoped | 個資法§27</t>
+        </is>
+      </c>
+      <c r="H8" s="28" t="inlineStr">
+        <is>
+          <t>TTX MSEL inject | Auto AAR report | Full GovOps</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>v2.2.0</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>GP2+GP3+GP4</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E8" s="27" t="inlineStr">
-        <is>
-          <t>🔲 planned</t>
-        </is>
-      </c>
-      <c r="F8" s="27" t="inlineStr">
-        <is>
-          <t>第一個可銷售版本，含部署維運完整支援</t>
-        </is>
-      </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>First sellable | Full deploy ops | GP4</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="inlineStr">
+        <is>
+          <t>TTX MSEL | Auto AAR</t>
+        </is>
+      </c>
+      <c r="I9" s="29" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>v3.0.0</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>GovOps + TTX</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>GP1–GP4</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>v3.0.0</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>GovOps + TTX</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr">
+        <is>
+          <t>GP1 TTX+MSEL+AAR closed | HSEEP/NIMS</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>🔲 planned</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="inlineStr">
-        <is>
-          <t>HSEEP 演習管理對齊；ICS/NIMS 作業流程支援</t>
-        </is>
-      </c>
-      <c r="G9" s="27" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>v3.1.0</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>GP1–GP4+AI</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>v3.1.0</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>AI differentiation</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G11" s="29" t="inlineStr">
+        <is>
+          <t>Silent Scribe | AI predict layer</t>
+        </is>
+      </c>
+      <c r="H11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
-        <is>
-          <t>🔲 planned</t>
-        </is>
-      </c>
-      <c r="F10" s="27" t="inlineStr">
-        <is>
-          <t>Silent Scribe STT；AI predict layer</t>
-        </is>
-      </c>
-      <c r="G10" s="27" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
+        <is>
+          <t>2027-Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>v3.2.0</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>Flagship + ISO</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>GP1–GP5</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>v3.2.0</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>Flagship + ISO</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G12" s="29" t="inlineStr">
+        <is>
+          <t>ISO 27001/CNS 27001 | GP5 real disaster</t>
+        </is>
+      </c>
+      <c r="H12" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
-        <is>
-          <t>🔲 planned</t>
-        </is>
-      </c>
-      <c r="F11" s="27" t="inlineStr">
-        <is>
-          <t>ISO 27001 / CNS 27001</t>
-        </is>
-      </c>
-      <c r="G11" s="27" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
+        <is>
+          <t>2027-Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>B.  v2.1.0 Execution Sequence (A → B → C → D → E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Seq</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>Blocks/Depends on</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>Deploy Infra</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>Structured logging + collect_debug.sh</t>
+        </is>
+      </c>
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G16" s="30" t="inlineStr">
+        <is>
+          <t>None — do first</t>
+        </is>
+      </c>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>Gate B diagnostics for all subsequent tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Deploy Infra</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>/health liveness endpoint</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G17" s="30" t="inlineStr">
+        <is>
+          <t>None — do first</t>
+        </is>
+      </c>
+      <c r="H17" s="30" t="inlineStr">
+        <is>
+          <t>Fresh install check; systemd watchdog</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>P0 Security</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>Pi first-run security</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>Issue → Capability Traceability Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>Issue#</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>CAP affected</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>GAP closed</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t>PR#</t>
-        </is>
-      </c>
-      <c r="G14" s="24" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>Closed date</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="29" t="inlineStr">
-        <is>
-          <t>#6</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>Pi first-run security</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>CAP-010 (FieldSync)</t>
-        </is>
-      </c>
-      <c r="D15" s="29" t="inlineStr">
-        <is>
-          <t>GAP-AUTH-PI-01</t>
-        </is>
-      </c>
-      <c r="E15" s="29" t="inlineStr">
-        <is>
-          <t>v0.13.0 + v2.1.0</t>
-        </is>
-      </c>
-      <c r="F15" s="29" t="inlineStr">
-        <is>
-          <t>#7</t>
-        </is>
-      </c>
-      <c r="G15" s="29" t="inlineStr">
-        <is>
-          <t>✅ closed</t>
-        </is>
-      </c>
-      <c r="H15" s="29" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
+        <is>
+          <t>PR#7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>P0 Security</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>#8</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>WebSocket pre-auth gate</t>
-        </is>
-      </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>CAP-013 (WSAuth), CAP-010</t>
-        </is>
-      </c>
-      <c r="D16" s="29" t="inlineStr">
-        <is>
-          <t>GAP-AUTH-02, GAP-SYNC-17</t>
-        </is>
-      </c>
-      <c r="E16" s="29" t="inlineStr">
-        <is>
-          <t>v2.1.0</t>
-        </is>
-      </c>
-      <c r="F16" s="29" t="inlineStr">
-        <is>
-          <t>#9</t>
-        </is>
-      </c>
-      <c r="G16" s="29" t="inlineStr">
-        <is>
-          <t>✅ closed</t>
-        </is>
-      </c>
-      <c r="H16" s="29" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>WS pre-auth gate</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="inlineStr">
+        <is>
+          <t>PR#9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>P0 Security</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>Trusted Ingest HMAC</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>CAP-012 (TrustedIngest), CAP-010</t>
-        </is>
-      </c>
-      <c r="D17" s="30" t="inlineStr">
-        <is>
-          <t>GAP-SYNC-05</t>
-        </is>
-      </c>
-      <c r="E17" s="30" t="inlineStr">
-        <is>
-          <t>v2.1.0</t>
-        </is>
-      </c>
-      <c r="F17" s="30" t="inlineStr">
-        <is>
-          <t>#12</t>
-        </is>
-      </c>
-      <c r="G17" s="30" t="inlineStr">
-        <is>
-          <t>🔄 in progress</t>
-        </is>
-      </c>
-      <c r="H17" s="30" t="inlineStr">
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="H20" s="28" t="inlineStr">
+        <is>
+          <t>PR#12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>P0 Security</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>Frontend modularise + CSP (CAP-035)</t>
+        </is>
+      </c>
+      <c r="E21" s="29" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F21" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G21" s="29" t="inlineStr">
+        <is>
+          <t>After #11 (Option beta)</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="inlineStr">
+        <is>
+          <t>Blocks RBAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>P0 Security</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>4-role RBAC + endpoint gate (CAP-014)</t>
+        </is>
+      </c>
+      <c r="E22" s="29" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F22" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G22" s="29" t="inlineStr">
+        <is>
+          <t>After CAP-035</t>
+        </is>
+      </c>
+      <c r="H22" s="29" t="inlineStr">
+        <is>
+          <t>Core security</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>P0 Security</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>WS full security / Encryption / Pi+PWA / DR drill</t>
+        </is>
+      </c>
+      <c r="E23" s="29" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F23" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G23" s="29" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="inlineStr">
+        <is>
+          <t>Multiple P0s</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>P1 Hardening</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>Session / rate limit / Pi key / SBOM / step-ca / config / IR plan</t>
+        </is>
+      </c>
+      <c r="E24" s="29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F24" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G24" s="29" t="inlineStr">
+        <is>
+          <t>After P0 all close</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="inlineStr">
+        <is>
+          <t>8 issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>COP redesign (heatmap + cluster + search + replay)</t>
+        </is>
+      </c>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F25" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G25" s="29" t="inlineStr">
+        <is>
+          <t>After P1 all close</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>Release Acceptance</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>GP2+GP3 E2E + Fresh install + Multi-Pi + Owner sign-off</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="inlineStr">
+        <is>
+          <t>After D</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="inlineStr">
+        <is>
+          <t>2 weeks before June exercise</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="8" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>C.  v2.1.0 Claims (only after Release Acceptance sign-off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>Allowed / Forbidden</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>Supports field drill (現場演練) procurement</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>ALLOWED</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>GP2+GP3 closed and Release Acceptance signed off</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>GP2 field report → COP → decision loop</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>ALLOWED</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>End-to-end verified in Seq E</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>GP3 offline → sync loop</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>ALLOWED</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>End-to-end verified in Seq E</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>NIST 800-53 Moderate (scoped, self-declared)</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>ALLOWED</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>After P0+P1 all close</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>Personal Data Act s.27 compliant</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>ALLOWED</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="inlineStr">
+        <is>
+          <t>After encryption + RBAC close</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>Appendix 10 — 12 items Moderate</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>ALLOWED</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>After all P0 close</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="33" t="inlineStr">
+        <is>
+          <t>TTX MSEL inject supported</t>
+        </is>
+      </c>
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>FORBIDDEN</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>v3.0.0 scope — NEVER claim for v2.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="33" t="inlineStr">
+        <is>
+          <t>Automatic AAR report generation</t>
+        </is>
+      </c>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>FORBIDDEN</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>v3.0.0 scope — NEVER claim for v2.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>Full formal exercise (正式演訓/TTX)</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>FORBIDDEN</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>v2.1.0 = field drill only. Use exact phrase "現場演練"</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1000,185 +1982,167 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="22" customWidth="1" style="6" min="1" max="1"/>
-    <col width="88" customWidth="1" style="6" min="2" max="2"/>
-    <col width="26" customWidth="1" style="6" min="4" max="4"/>
-    <col width="24" customWidth="1" style="6" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="6">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>ICS_DMAS Master Capability Matrix</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
-      <c r="G1" s="9" t="n"/>
-      <c r="H1" s="9" t="n"/>
-      <c r="I1" s="9" t="n"/>
-      <c r="J1" s="9" t="n"/>
-      <c r="K1" s="17" t="n"/>
-      <c r="L1" s="17" t="n"/>
-      <c r="M1" s="17" t="n"/>
-      <c r="N1" s="17" t="n"/>
-      <c r="O1" s="17" t="n"/>
-      <c r="P1" s="17" t="n"/>
-      <c r="Q1" s="17" t="n"/>
-      <c r="R1" s="17" t="n"/>
-      <c r="S1" s="17" t="n"/>
-      <c r="T1" s="17" t="n"/>
-      <c r="U1" s="17" t="n"/>
-      <c r="V1" s="17" t="n"/>
-      <c r="W1" s="17" t="n"/>
-      <c r="X1" s="17" t="n"/>
-      <c r="Y1" s="17" t="n"/>
-      <c r="Z1" s="17" t="n"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" s="6">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="4" t="n"/>
+      <c r="Y1" s="4" t="n"/>
+      <c r="Z1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>功能能力總矩陣：把功能、Golden Path、成熟度、版本 gate、資安/合規與驗收證據收斂為單一總控表。</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
-      <c r="G2" s="9" t="n"/>
-      <c r="H2" s="9" t="n"/>
-      <c r="I2" s="9" t="n"/>
-      <c r="J2" s="9" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>內容</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>公式/值</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>目的</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>作為產品、工程、資安、合規、業務與客戶驗收之共用 capability index。</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Total capabilities</t>
         </is>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="2">
         <f>COUNTA('Capability Matrix'!A2:A35)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Capability Matrix：每個 capability 一列，包含 Golden Path、maturity、acceptance、edition gate、security gate、evidence、claim。</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>P0 capabilities</t>
         </is>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="2">
         <f>COUNTIF('Capability Matrix'!S2:S35,"P0")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Golden Paths</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>GP1 TTX→AAR、GP2 現場回報→COP、GP3 離線同步→AAR、GP4 部署驗收、GP5 真實災害/IR/DR。</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Internal only rows</t>
         </is>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="2">
         <f>COUNTIF('Capability Matrix'!T2:T35,"Internal Only")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>優先 P0</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Trusted Ingest、WebSocket Pre-auth Gate、Pi/Field Node Sync、QR Offline Snapshot、TTX Inject、Edition Gate、Claim Guardrail。</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="2">
         <f>COUNTIF('Capability Matrix'!P2:P35,"Not Started")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>建議使用</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>用篩選器查看 P0、GP1、Exercise Pro、GovOps、L0/L1、Internal Only 等。</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Needs Hotfix / Hardening</t>
         </is>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="2">
         <f>COUNTIF('Capability Matrix'!P2:P35,"Needs*")</f>
         <v/>
       </c>
@@ -1202,3657 +2166,3720 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Z39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20"/>
   <cols>
-    <col width="12" customWidth="1" style="6" min="1" max="1"/>
-    <col width="24" customWidth="1" style="6" min="2" max="2"/>
-    <col width="20" customWidth="1" style="6" min="3" max="3"/>
-    <col width="42" customWidth="1" style="6" min="4" max="4"/>
-    <col width="18" customWidth="1" style="6" min="5" max="5"/>
-    <col width="22" customWidth="1" style="6" min="6" max="6"/>
-    <col width="16" customWidth="1" style="6" min="7" max="7"/>
-    <col width="16" customWidth="1" style="6" min="8" max="8"/>
-    <col width="55" customWidth="1" style="6" min="9" max="9"/>
-    <col width="22" customWidth="1" style="6" min="10" max="10"/>
-    <col width="40" customWidth="1" style="6" min="11" max="11"/>
-    <col width="32" customWidth="1" style="6" min="12" max="12"/>
-    <col width="22" customWidth="1" style="6" min="13" max="13"/>
-    <col width="45" customWidth="1" style="6" min="14" max="14"/>
-    <col width="36" customWidth="1" style="6" min="15" max="15"/>
-    <col width="18" customWidth="1" style="6" min="16" max="16"/>
-    <col width="42" customWidth="1" style="6" min="17" max="17"/>
-    <col width="22" customWidth="1" style="6" min="18" max="18"/>
-    <col width="10" customWidth="1" style="6" min="19" max="19"/>
-    <col width="22" customWidth="1" style="6" min="20" max="20"/>
+    <col width="21" customWidth="1" style="19" min="1" max="1"/>
+    <col width="27.1640625" customWidth="1" style="19" min="2" max="2"/>
+    <col width="27" customWidth="1" style="19" min="3" max="3"/>
+    <col width="42" customWidth="1" style="19" min="4" max="4"/>
+    <col width="18" customWidth="1" style="19" min="5" max="5"/>
+    <col width="22" customWidth="1" style="19" min="6" max="6"/>
+    <col width="16" customWidth="1" style="19" min="7" max="8"/>
+    <col width="55" customWidth="1" style="19" min="9" max="9"/>
+    <col width="29.83203125" customWidth="1" style="19" min="10" max="10"/>
+    <col width="57" customWidth="1" style="19" min="11" max="11"/>
+    <col width="32" customWidth="1" style="19" min="12" max="12"/>
+    <col width="22" customWidth="1" style="19" min="13" max="13"/>
+    <col width="45" customWidth="1" style="19" min="14" max="14"/>
+    <col width="36" customWidth="1" style="19" min="15" max="15"/>
+    <col width="18" customWidth="1" style="19" min="16" max="16"/>
+    <col width="44.83203125" customWidth="1" style="19" min="17" max="17"/>
+    <col width="22" customWidth="1" style="19" min="18" max="18"/>
+    <col width="10" customWidth="1" style="19" min="19" max="19"/>
+    <col width="39.83203125" customWidth="1" style="19" min="20" max="20"/>
+    <col width="8.83203125" customWidth="1" style="19" min="21" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="6">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Capability Matrix</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
-      <c r="G1" s="9" t="n"/>
-      <c r="H1" s="9" t="n"/>
-      <c r="I1" s="9" t="n"/>
-      <c r="J1" s="9" t="n"/>
-      <c r="K1" s="9" t="n"/>
-      <c r="L1" s="9" t="n"/>
-      <c r="M1" s="9" t="n"/>
-      <c r="N1" s="9" t="n"/>
-      <c r="O1" s="9" t="n"/>
-      <c r="P1" s="9" t="n"/>
-      <c r="Q1" s="9" t="n"/>
-      <c r="R1" s="9" t="n"/>
-      <c r="S1" s="9" t="n"/>
-      <c r="T1" s="9" t="n"/>
-      <c r="U1" s="17" t="n"/>
-      <c r="V1" s="17" t="n"/>
-      <c r="W1" s="17" t="n"/>
-      <c r="X1" s="17" t="n"/>
-      <c r="Y1" s="17" t="n"/>
-      <c r="Z1" s="17" t="n"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" s="6">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="U1" s="18" t="n"/>
+      <c r="V1" s="18" t="n"/>
+      <c r="W1" s="18" t="n"/>
+      <c r="X1" s="18" t="n"/>
+      <c r="Y1" s="18" t="n"/>
+      <c r="Z1" s="18" t="n"/>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>主表：每列是一項能力，連結 Golden Path、成熟度、版本、資安/合規 gate、驗收證據與下一步。</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
-      <c r="G2" s="9" t="n"/>
-      <c r="H2" s="9" t="n"/>
-      <c r="I2" s="9" t="n"/>
-      <c r="J2" s="9" t="n"/>
-      <c r="K2" s="9" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="M2" s="9" t="n"/>
-      <c r="N2" s="9" t="n"/>
-      <c r="O2" s="9" t="n"/>
-      <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="9" t="n"/>
-      <c r="R2" s="9" t="n"/>
-      <c r="S2" s="9" t="n"/>
-      <c r="T2" s="9" t="n"/>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="42" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Capability ID</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Capability</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>Capability Group</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>Golden Path(s)</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>Primary User(s)</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>Current Maturity</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t>Target Maturity</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>Edition Gate</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="21" t="inlineStr">
         <is>
           <t>Security Gate / Dependency</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t>Compliance Mapping</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="M4" s="21" t="inlineStr">
         <is>
           <t>Data Sensitivity</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t>Evidence Required</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="21" t="inlineStr">
         <is>
           <t>External Claim</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="Q4" s="21" t="inlineStr">
         <is>
           <t>Next Action</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="S4" s="21" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="T4" s="21" t="inlineStr">
         <is>
           <t>Disclosure</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1" s="6">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>CAP-001</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>TTX Scenario Database</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>TTX / Exercise</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>建立、版本化與載入演訓劇本、情境庫、注入時間軸。</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>GP1</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>演訓導控、PM</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>可建立劇本、版本、inject 清單；可載入場次；可匯出劇本摘要。</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>需 session 隔離；資料不可污染 real session。</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>HSEEP / MSEL alignment</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="M5" s="22" t="inlineStr">
         <is>
           <t>Low–Medium：演訓資料</t>
         </is>
       </c>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="N5" s="22" t="inlineStr">
         <is>
           <t>劇本匯出、場次紀錄、操作截圖</t>
         </is>
       </c>
-      <c r="O5" s="14" t="inlineStr">
+      <c r="O5" s="22" t="inlineStr">
         <is>
           <t>支援受控 TTX 劇本管理</t>
         </is>
       </c>
-      <c r="P5" s="14" t="inlineStr">
+      <c r="P5" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q5" s="14" t="inlineStr">
+      <c r="Q5" s="22" t="inlineStr">
         <is>
           <t>定義劇本 schema、版本規則與 import/export</t>
         </is>
       </c>
-      <c r="R5" s="14" t="inlineStr">
+      <c r="R5" s="22" t="inlineStr">
         <is>
           <t>Product / TTX</t>
         </is>
       </c>
-      <c r="S5" s="14" t="inlineStr">
+      <c r="S5" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T5" s="14" t="inlineStr">
+      <c r="T5" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1" s="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>CAP-002</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>TTX Inject</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>TTX / Exercise</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>依時間、對象、條件注入狀況，記錄送達、閱讀與回應。</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>GP1</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>演訓導控、各組操作員</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>可排程、指定對象、記錄送達/閱讀/回應；L3 需 inject 簽章與 audit。</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>Trusted Ingest；inject signature；TTX/real session mutex。</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>HSEEP / MSEL</t>
         </is>
       </c>
-      <c r="M6" s="14" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t>Medium：演訓導控資料</t>
         </is>
       </c>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="N6" s="22" t="inlineStr">
         <is>
           <t>inject log、audit log、簽章驗證測試</t>
         </is>
       </c>
-      <c r="O6" s="14" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t>支援 MSEL 式狀況注入</t>
         </is>
       </c>
-      <c r="P6" s="14" t="inlineStr">
+      <c r="P6" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q6" s="14" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t>補 inject 簽章、read receipt、session mutex 驗收</t>
         </is>
       </c>
-      <c r="R6" s="14" t="inlineStr">
+      <c r="R6" s="22" t="inlineStr">
         <is>
           <t>TTX / Security</t>
         </is>
       </c>
-      <c r="S6" s="14" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="T6" s="14" t="inlineStr">
+      <c r="T6" s="22" t="inlineStr">
         <is>
           <t>Internal + Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1" s="6">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>CAP-003</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>TTX Session Control</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>TTX / Exercise</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>演訓場次啟動、暫停、加速、結束、封存與 real session 隔離。</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>GP1</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>演訓導控、PM</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>場次狀態可切換；real/TTX 資料硬隔離；封存後不可竄改。</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>session mutex；RBAC；audit evidence。</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>HSEEP / AAR-IP</t>
         </is>
       </c>
-      <c r="M7" s="14" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N7" s="14" t="inlineStr">
+      <c r="N7" s="22" t="inlineStr">
         <is>
           <t>session 狀態紀錄、隔離測試、封存紀錄</t>
         </is>
       </c>
-      <c r="O7" s="14" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t>支援受控演訓場次管理</t>
         </is>
       </c>
-      <c r="P7" s="14" t="inlineStr">
+      <c r="P7" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q7" s="14" t="inlineStr">
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t>明確 TTX session lifecycle 與封存規則</t>
         </is>
       </c>
-      <c r="R7" s="14" t="inlineStr">
+      <c r="R7" s="22" t="inlineStr">
         <is>
           <t>Product / Backend</t>
         </is>
       </c>
-      <c r="S7" s="14" t="inlineStr">
+      <c r="S7" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T7" s="14" t="inlineStr">
+      <c r="T7" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1" s="6">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>CAP-004</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Command COP</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Command / COP</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>指揮官態勢總覽：事件、資源、異常、來源時間、告警與趨勢。</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>GP2</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>指揮官、幕僚</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>10 秒內看見關鍵態勢；事件/資源/異常有來源時間；可篩選與 drill-down。</t>
         </is>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro</t>
         </is>
       </c>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>snapshot/sync 需可信；資料衝突需標示。</t>
         </is>
       </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>NIMS Communications &amp; Information Management</t>
         </is>
       </c>
-      <c r="M8" s="14" t="inlineStr">
+      <c r="M8" s="22" t="inlineStr">
         <is>
           <t>Medium–High：視輸入資料</t>
         </is>
       </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="N8" s="22" t="inlineStr">
         <is>
           <t>UI 截圖、E2E 測試、資料來源標記</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="O8" s="22" t="inlineStr">
         <is>
           <t>支援受控演訓 COP</t>
         </is>
       </c>
-      <c r="P8" s="14" t="inlineStr">
+      <c r="P8" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q8" s="14" t="inlineStr">
+      <c r="Q8" s="22" t="inlineStr">
         <is>
           <t>定義 COP 最小資訊架構與衝突提示</t>
         </is>
       </c>
-      <c r="R8" s="14" t="inlineStr">
+      <c r="R8" s="22" t="inlineStr">
         <is>
           <t>Product / Frontend</t>
         </is>
       </c>
-      <c r="S8" s="14" t="inlineStr">
+      <c r="S8" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T8" s="14" t="inlineStr">
+      <c r="T8" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1" s="6">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>CAP-005</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Event Timeline</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Command / COP</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>將 inject、現場回報、決策、任務、同步事件串成時間線。</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>GP1, GP2, GP3</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>指揮官、AAR 分析者</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>可按時間重建事件；L3 需區分當時已知與事後補充。</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K9" s="14" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>audit log；clock sync；trusted ingest。</t>
         </is>
       </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr">
         <is>
           <t>ICS 214 / AAR evidence</t>
         </is>
       </c>
-      <c r="M9" s="14" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t>Medium–High</t>
         </is>
       </c>
-      <c r="N9" s="14" t="inlineStr">
+      <c r="N9" s="22" t="inlineStr">
         <is>
           <t>timeline 匯出、audit 對照、回放測試</t>
         </is>
       </c>
-      <c r="O9" s="14" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t>支援演訓事件時間線</t>
         </is>
       </c>
-      <c r="P9" s="14" t="inlineStr">
+      <c r="P9" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q9" s="14" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t>建立 timeline source model 與 replay view</t>
         </is>
       </c>
-      <c r="R9" s="14" t="inlineStr">
+      <c r="R9" s="22" t="inlineStr">
         <is>
           <t>Backend / AAR</t>
         </is>
       </c>
-      <c r="S9" s="14" t="inlineStr">
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T9" s="14" t="inlineStr">
+      <c r="T9" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1" s="6">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>CAP-006</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Decision Record</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Command / Workflow</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>記錄決策者、時間、依據、決策內容、影響事件與後續任務。</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>GP1, GP2</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>指揮官、幕僚</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>可建立決策、關聯事件/任務、記錄依據；L3 需 audit 與 AAR 可追溯。</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="K10" s="14" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>RBAC；audit evidence；Unity of Command。</t>
         </is>
       </c>
-      <c r="L10" s="14" t="inlineStr">
+      <c r="L10" s="22" t="inlineStr">
         <is>
           <t>ICS 214 / NIMS Command &amp; Coordination</t>
         </is>
       </c>
-      <c r="M10" s="14" t="inlineStr">
+      <c r="M10" s="22" t="inlineStr">
         <is>
           <t>High：決策責任資料</t>
         </is>
       </c>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="N10" s="22" t="inlineStr">
         <is>
           <t>決策紀錄、AAR link、audit trail</t>
         </is>
       </c>
-      <c r="O10" s="14" t="inlineStr">
+      <c r="O10" s="22" t="inlineStr">
         <is>
           <t>可支援決策紀錄與 AAR 追溯</t>
         </is>
       </c>
-      <c r="P10" s="14" t="inlineStr">
+      <c r="P10" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q10" s="14" t="inlineStr">
+      <c r="Q10" s="22" t="inlineStr">
         <is>
           <t>定義 decision schema 與與 event/task 關聯</t>
         </is>
       </c>
-      <c r="R10" s="14" t="inlineStr">
+      <c r="R10" s="22" t="inlineStr">
         <is>
           <t>Product / Backend</t>
         </is>
       </c>
-      <c r="S10" s="14" t="inlineStr">
+      <c r="S10" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T10" s="14" t="inlineStr">
+      <c r="T10" s="22" t="inlineStr">
         <is>
           <t>Internal + Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1" s="6">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>CAP-007</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Task Assignment</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>Command / Workflow</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>決策後產生任務，指定責任組、期限、狀態與完成回報。</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>GP2</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>指揮官、組長、操作員</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>可建立/指派/更新/結案任務；現場可回報完成。</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K11" s="14" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>RBAC；audit log；notification。</t>
         </is>
       </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="L11" s="22" t="inlineStr">
         <is>
           <t>NIMS Resource Management</t>
         </is>
       </c>
-      <c r="M11" s="14" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N11" s="14" t="inlineStr">
+      <c r="N11" s="22" t="inlineStr">
         <is>
           <t>任務測試、狀態轉換紀錄</t>
         </is>
       </c>
-      <c r="O11" s="14" t="inlineStr">
+      <c r="O11" s="22" t="inlineStr">
         <is>
           <t>支援受控演訓任務追蹤</t>
         </is>
       </c>
-      <c r="P11" s="14" t="inlineStr">
+      <c r="P11" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q11" s="14" t="inlineStr">
+      <c r="Q11" s="22" t="inlineStr">
         <is>
           <t>定義最小 task lifecycle：open/assigned/done/closed</t>
         </is>
       </c>
-      <c r="R11" s="14" t="inlineStr">
+      <c r="R11" s="22" t="inlineStr">
         <is>
           <t>Product / Backend</t>
         </is>
       </c>
-      <c r="S11" s="14" t="inlineStr">
+      <c r="S11" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="T11" s="14" t="inlineStr">
+      <c r="T11" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1" s="6">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>CAP-008</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>PWA Field Report</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Field / PWA</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>收容、醫療、前進組等現場填報資料，支援低負擔輸入。</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>GP2, GP3</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>現場操作員、志工</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>可離線填報、暫存、送出狀態明確；資料格式可被 COP 採用。</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro</t>
         </is>
       </c>
-      <c r="K12" s="14" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>PII policy；input validation；sync signing。</t>
         </is>
       </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="L12" s="22" t="inlineStr">
         <is>
           <t>NIMS Information Management / PII policy</t>
         </is>
       </c>
-      <c r="M12" s="14" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t>Medium–High：可能含個資/醫療</t>
         </is>
       </c>
-      <c r="N12" s="14" t="inlineStr">
+      <c r="N12" s="22" t="inlineStr">
         <is>
           <t>PWA E2E 測試、離線測試、資料欄位清單</t>
         </is>
       </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t>支援現場受控回報</t>
         </is>
       </c>
-      <c r="P12" s="14" t="inlineStr">
+      <c r="P12" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q12" s="14" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t>定義採納/退回/修正流程與 UI 狀態</t>
         </is>
       </c>
-      <c r="R12" s="14" t="inlineStr">
+      <c r="R12" s="22" t="inlineStr">
         <is>
           <t>PWA / Product</t>
         </is>
       </c>
-      <c r="S12" s="14" t="inlineStr">
+      <c r="S12" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T12" s="14" t="inlineStr">
+      <c r="T12" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="70" customHeight="1" s="6">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>CAP-009</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Report Adoption Workflow</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Field / Data Quality</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>現場回報進 COP 前的採納、退回、修正與衝突裁決流程。</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>GP2, GP3</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>幕僚、組長、指揮官</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>每筆回報有 pending/accepted/rejected/superseded 狀態；採納者與理由可追溯。</t>
         </is>
       </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="K13" s="14" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>RBAC；audit；trusted ingest；conflict resolution。</t>
         </is>
       </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr">
         <is>
           <t>NIMS Information Management / AAR evidence</t>
         </is>
       </c>
-      <c r="M13" s="14" t="inlineStr">
+      <c r="M13" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N13" s="14" t="inlineStr">
+      <c r="N13" s="22" t="inlineStr">
         <is>
           <t>採納流程測試、audit trail、衝突案例</t>
         </is>
       </c>
-      <c r="O13" s="14" t="inlineStr">
+      <c r="O13" s="22" t="inlineStr">
         <is>
           <t>可支援資料採納與追溯</t>
         </is>
       </c>
-      <c r="P13" s="14" t="inlineStr">
+      <c r="P13" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q13" s="14" t="inlineStr">
+      <c r="Q13" s="22" t="inlineStr">
         <is>
           <t>新增 adoption_status 與 conflict resolution 規格</t>
         </is>
       </c>
-      <c r="R13" s="14" t="inlineStr">
+      <c r="R13" s="22" t="inlineStr">
         <is>
           <t>Product / Backend</t>
         </is>
       </c>
-      <c r="S13" s="14" t="inlineStr">
+      <c r="S13" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T13" s="14" t="inlineStr">
+      <c r="T13" s="22" t="inlineStr">
         <is>
           <t>Internal + Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="70" customHeight="1" s="6">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>CAP-010</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>Pi / Field Node Sync</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>Field / Sync</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>Pi 或 Field Node 與 Command Dashboard 之間的現場同步能力。</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>GP2, GP3</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>現場節點、維運</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>可同步狀態；L3 需 node identity、key rotation、replay protection。</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>GovOps / Tactical</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
-        <is>
-          <t>Pi first-run ✅ (#6/PR#7)；WS gate ✅ (#8/PR#9)；HMAC 🔄 (#11/PR#12)；API key hash 🔲</t>
-        </is>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>PI-01 CLOSED #6/PR#7; WS-01 CLOSED #8/PR#9; HMAC IN PROGRESS #11/PR#12; API key hash TBD</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
         <is>
           <t>NIST SC / IA / OT-like deployment</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr">
+      <c r="M14" s="22" t="inlineStr">
         <is>
           <t>High：同步與節點密鑰</t>
         </is>
       </c>
-      <c r="N14" s="14" t="inlineStr">
-        <is>
-          <t>PR#7 (PI-01 close 2026-04-26)；PR#9 (WS-01 close 2026-04-26)；#11 TI-01 in progress</t>
-        </is>
-      </c>
-      <c r="O14" s="14" t="inlineStr">
+      <c r="N14" s="22" t="inlineStr">
+        <is>
+          <t>PR#7 PI-01 closed 2026-04-26; PR#9 WS-01 closed 2026-04-26; #11 TI-01 in progress PR#12</t>
+        </is>
+      </c>
+      <c r="O14" s="22" t="inlineStr">
         <is>
           <t>支援現場節點同步</t>
         </is>
       </c>
-      <c r="P14" s="14" t="inlineStr">
+      <c r="P14" s="22" t="inlineStr">
         <is>
           <t>Partial Hardened</t>
         </is>
       </c>
-      <c r="Q14" s="14" t="inlineStr">
-        <is>
-          <t>待 #11 (TI-01) close 後評估升 L2</t>
-        </is>
-      </c>
-      <c r="R14" s="14" t="inlineStr">
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>Pending #11 (TI-01) close then evaluate L2</t>
+        </is>
+      </c>
+      <c r="R14" s="22" t="inlineStr">
         <is>
           <t>Backend / Node / Security</t>
         </is>
       </c>
-      <c r="S14" s="14" t="inlineStr">
+      <c r="S14" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="T14" s="14" t="inlineStr">
+      <c r="T14" s="22" t="inlineStr">
         <is>
           <t>Internal Only</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="70" customHeight="1" s="6">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>CAP-011</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>QR Offline Snapshot</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>Field / Offline</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>斷網時產生/掃描 QR 快照，以離線方式匯入重要狀態。</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>GP3</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>現場操作員、幕僚</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>可離線匯入；L3 需簽章、nonce、防重放、來源標示。</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K15" s="14" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>Trusted Ingest；QR signature；replay cache。</t>
         </is>
       </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>NIMS resiliency / AAR evidence</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr">
         <is>
           <t>Medium–High</t>
         </is>
       </c>
-      <c r="N15" s="14" t="inlineStr">
+      <c r="N15" s="22" t="inlineStr">
         <is>
           <t>QR 匯入測試、簽章驗證、重放拒收測試</t>
         </is>
       </c>
-      <c r="O15" s="14" t="inlineStr">
+      <c r="O15" s="22" t="inlineStr">
         <is>
           <t>支援斷網備援回報</t>
         </is>
       </c>
-      <c r="P15" s="14" t="inlineStr">
+      <c r="P15" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q15" s="14" t="inlineStr">
+      <c r="Q15" s="22" t="inlineStr">
         <is>
           <t>定義 QR payload 格式與驗證流程</t>
         </is>
       </c>
-      <c r="R15" s="14" t="inlineStr">
+      <c r="R15" s="22" t="inlineStr">
         <is>
           <t>PWA / Backend / Security</t>
         </is>
       </c>
-      <c r="S15" s="14" t="inlineStr">
+      <c r="S15" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="T15" s="14" t="inlineStr">
+      <c r="T15" s="22" t="inlineStr">
         <is>
           <t>Internal + Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1" s="6">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>CAP-012</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Snapshot / Sync Trusted Ingest</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>Security / Data Integrity</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>所有 snapshot、sync_push、QR、inject 的簽章、nonce、timestamp 與防重放控制。</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>GP1, GP2, GP3</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>後端、資安、架構師</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>未簽章資料拒收；重放拒收；body 變更簽章失效；key_id 可追溯。</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J16" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>HMAC/signature；nonce cache；timestamp skew；key rotation。</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="L16" s="22" t="inlineStr">
         <is>
           <t>NIST IA/SC/SI / Data integrity</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr">
+      <c r="M16" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>#11 Trusted Ingest HMAC in progress (PR#12)</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
+      <c r="N16" s="22" t="inlineStr">
+        <is>
+          <t>#11 Trusted Ingest HMAC in progress PR#12</t>
+        </is>
+      </c>
+      <c r="O16" s="22" t="inlineStr">
         <is>
           <t>已具資料完整性控制（完成後才可說）</t>
         </is>
       </c>
-      <c r="P16" s="14" t="inlineStr">
+      <c r="P16" s="22" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="Q16" s="14" t="inlineStr">
-        <is>
-          <t>#11 TI-01 open (PR#12 in progress)；close 後評估升 L2</t>
-        </is>
-      </c>
-      <c r="R16" s="14" t="inlineStr">
+      <c r="Q16" s="22" t="inlineStr">
+        <is>
+          <t>#11 TI-01 open (PR#12 in progress); close then evaluate L2</t>
+        </is>
+      </c>
+      <c r="R16" s="22" t="inlineStr">
         <is>
           <t>Security / Backend</t>
         </is>
       </c>
-      <c r="S16" s="14" t="inlineStr">
+      <c r="S16" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="T16" s="14" t="inlineStr">
+      <c r="T16" s="22" t="inlineStr">
         <is>
           <t>Internal Only</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1" s="6">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>CAP-013</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>WebSocket Pre-auth Gate</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>Security / Sync</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>WebSocket 狀態改變訊息必須先通過 server-side auth gate。</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>GP2, GP3</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>後端、Node、資安</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>未 auth client 送 delta/sync_push/clear_table 必須拒絕；禁止 client 自報 role。</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>WS auth gate；server-side session；role gate。</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>NIST AC/IA/SC</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N17" s="14" t="inlineStr">
-        <is>
-          <t>PR#9 (WS-01 close 2026-04-26)；WS tests 19/19 pass</t>
-        </is>
-      </c>
-      <c r="O17" s="14" t="inlineStr">
+      <c r="N17" s="22" t="inlineStr">
+        <is>
+          <t>PR#9 WS-01 closed 2026-04-26; 19/19 unit tests pass</t>
+        </is>
+      </c>
+      <c r="O17" s="22" t="inlineStr">
         <is>
           <t>不建議外部宣稱細節</t>
         </is>
       </c>
-      <c r="P17" s="14" t="inlineStr">
+      <c r="P17" s="22" t="inlineStr">
         <is>
           <t>Partial Hardened</t>
         </is>
       </c>
-      <c r="Q17" s="14" t="inlineStr">
-        <is>
-          <t>待 #11 (TI-01) close 後評估升 L2</t>
-        </is>
-      </c>
-      <c r="R17" s="14" t="inlineStr">
+      <c r="Q17" s="22" t="inlineStr">
+        <is>
+          <t>Pending #11 (TI-01) close then evaluate L2</t>
+        </is>
+      </c>
+      <c r="R17" s="22" t="inlineStr">
         <is>
           <t>Node / Security</t>
         </is>
       </c>
-      <c r="S17" s="14" t="inlineStr">
+      <c r="S17" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="T17" s="14" t="inlineStr">
+      <c r="T17" s="22" t="inlineStr">
         <is>
           <t>Internal Only</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="70" customHeight="1" s="6">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>CAP-014</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>RBAC / Endpoint Gate</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>Security / Auth</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>後端角色權限控管，避免只靠前端或 session-level auth。</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>全部</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>系統管理員、所有使用者</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>每個 state-changing endpoint 有 role gate；角色變更立即 revoke session。</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="J18" s="22" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="K18" s="14" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>C1-A Phase 2；session revoke；least privilege。</t>
         </is>
       </c>
-      <c r="L18" s="14" t="inlineStr">
+      <c r="L18" s="22" t="inlineStr">
         <is>
           <t>NIST AC / IA</t>
         </is>
       </c>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="M18" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N18" s="14" t="inlineStr">
+      <c r="N18" s="22" t="inlineStr">
         <is>
           <t>RBAC matrix、API tests、session revoke tests</t>
         </is>
       </c>
-      <c r="O18" s="14" t="inlineStr">
+      <c r="O18" s="22" t="inlineStr">
         <is>
           <t>支援角色權限控管（完成後）</t>
         </is>
       </c>
-      <c r="P18" s="14" t="inlineStr">
+      <c r="P18" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q18" s="14" t="inlineStr">
+      <c r="Q18" s="22" t="inlineStr">
         <is>
           <t>定義角色 enum、endpoint map 與測試</t>
         </is>
       </c>
-      <c r="R18" s="14" t="inlineStr">
+      <c r="R18" s="22" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="S18" s="14" t="inlineStr">
+      <c r="S18" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T18" s="14" t="inlineStr">
+      <c r="T18" s="22" t="inlineStr">
         <is>
           <t>Internal + Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="70" customHeight="1" s="6">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>CAP-015</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>Audit Evidence</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>Security / Audit</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>重要操作、資料採納、決策、匯出與 admin 行為的稽核證據。</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>GP1, GP2, GP3, GP4, GP5</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>資安、PM、客戶驗收</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>所有重要操作可追溯；L3 需 hash chain、append-only、correlation ID。</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>C1-D；不可刪改；retention；correlation ID。</t>
         </is>
       </c>
-      <c r="L19" s="14" t="inlineStr">
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>NIST AU / ICS 214 / AAR evidence</t>
         </is>
       </c>
-      <c r="M19" s="14" t="inlineStr">
+      <c r="M19" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N19" s="14" t="inlineStr">
+      <c r="N19" s="22" t="inlineStr">
         <is>
           <t>audit log、hash chain 驗證、reset 不刪 log 測試</t>
         </is>
       </c>
-      <c r="O19" s="14" t="inlineStr">
+      <c r="O19" s="22" t="inlineStr">
         <is>
           <t>支援稽核追溯（完成後）</t>
         </is>
       </c>
-      <c r="P19" s="14" t="inlineStr">
+      <c r="P19" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q19" s="14" t="inlineStr">
+      <c r="Q19" s="22" t="inlineStr">
         <is>
           <t>補 hash chain 與禁止 reset 刪 audit</t>
         </is>
       </c>
-      <c r="R19" s="14" t="inlineStr">
+      <c r="R19" s="22" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="S19" s="14" t="inlineStr">
+      <c r="S19" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T19" s="14" t="inlineStr">
+      <c r="T19" s="22" t="inlineStr">
         <is>
           <t>Internal + Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="70" customHeight="1" s="6">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>CAP-016</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>AAR Timeline</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>AAR</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>從事件、回報、決策與 inject 產生 AAR 時間線。</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>GP1, GP3</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>演訓顧問、PM、客戶</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>時間線可重建；每個節點有來源、時間、責任；L3 可回點原始證據。</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J20" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K20" s="14" t="inlineStr">
+      <c r="K20" s="22" t="inlineStr">
         <is>
           <t>audit evidence；AAR reproducibility；source provenance。</t>
         </is>
       </c>
-      <c r="L20" s="14" t="inlineStr">
+      <c r="L20" s="22" t="inlineStr">
         <is>
           <t>HSEEP AAR/IP / ICS 214</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr">
+      <c r="M20" s="22" t="inlineStr">
         <is>
           <t>Medium–High</t>
         </is>
       </c>
-      <c r="N20" s="14" t="inlineStr">
+      <c r="N20" s="22" t="inlineStr">
         <is>
           <t>AAR 匯出、source link、replay 測試</t>
         </is>
       </c>
-      <c r="O20" s="14" t="inlineStr">
+      <c r="O20" s="22" t="inlineStr">
         <is>
           <t>支援 AAR 時間線</t>
         </is>
       </c>
-      <c r="P20" s="14" t="inlineStr">
+      <c r="P20" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q20" s="14" t="inlineStr">
+      <c r="Q20" s="22" t="inlineStr">
         <is>
           <t>定義 AAR source map 與回點機制</t>
         </is>
       </c>
-      <c r="R20" s="14" t="inlineStr">
+      <c r="R20" s="22" t="inlineStr">
         <is>
           <t>AAR / Product</t>
         </is>
       </c>
-      <c r="S20" s="14" t="inlineStr">
+      <c r="S20" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T20" s="14" t="inlineStr">
+      <c r="T20" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="70" customHeight="1" s="6">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="21" ht="70" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>CAP-017</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>AAR Improvement Plan</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>AAR</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>從演訓發現產生改善事項、責任人、期限與追蹤狀態。</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>GP1</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>演訓顧問、承辦、客戶主管</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>可建立 issue、assign owner、due date、status，匯出改善計畫。</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>與 AAR 結論需有來源；需權限控管。</t>
         </is>
       </c>
-      <c r="L21" s="14" t="inlineStr">
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>HSEEP AAR/IP</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr">
+      <c r="M21" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N21" s="14" t="inlineStr">
+      <c r="N21" s="22" t="inlineStr">
         <is>
           <t>改善計畫匯出、狀態追蹤測試</t>
         </is>
       </c>
-      <c r="O21" s="14" t="inlineStr">
+      <c r="O21" s="22" t="inlineStr">
         <is>
           <t>支援演訓改善事項追蹤</t>
         </is>
       </c>
-      <c r="P21" s="14" t="inlineStr">
+      <c r="P21" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q21" s="14" t="inlineStr">
+      <c r="Q21" s="22" t="inlineStr">
         <is>
           <t>定義 improvement item schema 與匯出格式</t>
         </is>
       </c>
-      <c r="R21" s="14" t="inlineStr">
+      <c r="R21" s="22" t="inlineStr">
         <is>
           <t>AAR / Product</t>
         </is>
       </c>
-      <c r="S21" s="14" t="inlineStr">
+      <c r="S21" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="T21" s="14" t="inlineStr">
+      <c r="T21" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="70" customHeight="1" s="6">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="22" ht="70" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>CAP-018</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>HSEEP / MSEL / AAR Alignment</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>Compliance / Exercise</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>將 TTX 注入、AAR、改善計畫對齊 HSEEP/MSEL/AAR-IP 流程。</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>GP1, GP4</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>演訓顧問、標案、PM</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>MSEL 欄位對照、AAR/IP 模板、可產生採購/演訓附件。</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="K22" s="14" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>claim language：只能說對齊/參考，不能說 certified。</t>
         </is>
       </c>
-      <c r="L22" s="14" t="inlineStr">
+      <c r="L22" s="22" t="inlineStr">
         <is>
           <t>HSEEP / MSEL / AAR-IP</t>
         </is>
       </c>
-      <c r="M22" s="14" t="inlineStr">
+      <c r="M22" s="22" t="inlineStr">
         <is>
           <t>Low–Medium</t>
         </is>
       </c>
-      <c r="N22" s="14" t="inlineStr">
+      <c r="N22" s="22" t="inlineStr">
         <is>
           <t>對照表、範本匯出、演訓報告</t>
         </is>
       </c>
-      <c r="O22" s="14" t="inlineStr">
+      <c r="O22" s="22" t="inlineStr">
         <is>
           <t>參考 HSEEP 流程並支援 AAR/IP 類輸出</t>
         </is>
       </c>
-      <c r="P22" s="14" t="inlineStr">
+      <c r="P22" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q22" s="14" t="inlineStr">
+      <c r="Q22" s="22" t="inlineStr">
         <is>
           <t>建立欄位 mapping 與範本</t>
         </is>
       </c>
-      <c r="R22" s="14" t="inlineStr">
+      <c r="R22" s="22" t="inlineStr">
         <is>
           <t>Compliance / TTX</t>
         </is>
       </c>
-      <c r="S22" s="14" t="inlineStr">
+      <c r="S22" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T22" s="14" t="inlineStr">
+      <c r="T22" s="22" t="inlineStr">
         <is>
           <t>Public / Sales Safe</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="70" customHeight="1" s="6">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="23" ht="70" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>CAP-019</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>Resource Status Tracking</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>追蹤床位、物資、醫療量能、人力等狀態。</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>GP2</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>幕僚、組長、指揮官</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>資源狀態可更新、顯示趨勢、標示來源時間；基本異常提示。</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>Trusted ingest；input validation。</t>
         </is>
       </c>
-      <c r="L23" s="14" t="inlineStr">
+      <c r="L23" s="22" t="inlineStr">
         <is>
           <t>NIMS Resource Management</t>
         </is>
       </c>
-      <c r="M23" s="14" t="inlineStr">
+      <c r="M23" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N23" s="14" t="inlineStr">
+      <c r="N23" s="22" t="inlineStr">
         <is>
           <t>狀態更新測試、COP 顯示、來源紀錄</t>
         </is>
       </c>
-      <c r="O23" s="14" t="inlineStr">
+      <c r="O23" s="22" t="inlineStr">
         <is>
           <t>支援資源狀態追蹤</t>
         </is>
       </c>
-      <c r="P23" s="14" t="inlineStr">
+      <c r="P23" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q23" s="14" t="inlineStr">
+      <c r="Q23" s="22" t="inlineStr">
         <is>
           <t>補資料來源與衝突標示</t>
         </is>
       </c>
-      <c r="R23" s="14" t="inlineStr">
+      <c r="R23" s="22" t="inlineStr">
         <is>
           <t>Product / Backend</t>
         </is>
       </c>
-      <c r="S23" s="14" t="inlineStr">
+      <c r="S23" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T23" s="14" t="inlineStr">
+      <c r="T23" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="70" customHeight="1" s="6">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="24" ht="70" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>CAP-020</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>Resource Request / Dispatch</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>Resource</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>資源請求、核准、派遣、狀態變更與釋回。</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>GP2</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>指揮官、幕僚、組長</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>需求→請求→指派→執行→回報→結案；L3 需可匯出資源紀錄。</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="K24" s="14" t="inlineStr">
+      <c r="K24" s="22" t="inlineStr">
         <is>
           <t>RBAC；audit；resource typing。</t>
         </is>
       </c>
-      <c r="L24" s="14" t="inlineStr">
+      <c r="L24" s="22" t="inlineStr">
         <is>
           <t>ICS 213RR / ICS 210 / NIMS Resource Management</t>
         </is>
       </c>
-      <c r="M24" s="14" t="inlineStr">
+      <c r="M24" s="22" t="inlineStr">
         <is>
           <t>Medium–High</t>
         </is>
       </c>
-      <c r="N24" s="14" t="inlineStr">
+      <c r="N24" s="22" t="inlineStr">
         <is>
           <t>資源請求流程測試、報表、audit</t>
         </is>
       </c>
-      <c r="O24" s="14" t="inlineStr">
+      <c r="O24" s="22" t="inlineStr">
         <is>
           <t>支援資源請求與派遣（完成後）</t>
         </is>
       </c>
-      <c r="P24" s="14" t="inlineStr">
+      <c r="P24" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q24" s="14" t="inlineStr">
+      <c r="Q24" s="22" t="inlineStr">
         <is>
           <t>先定最小 resource request workflow</t>
         </is>
       </c>
-      <c r="R24" s="14" t="inlineStr">
+      <c r="R24" s="22" t="inlineStr">
         <is>
           <t>Product / Backend</t>
         </is>
       </c>
-      <c r="S24" s="14" t="inlineStr">
+      <c r="S24" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="T24" s="14" t="inlineStr">
+      <c r="T24" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="70" customHeight="1" s="6">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="25" ht="70" customHeight="1">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>CAP-021</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Operational Period</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>ICS / Workflow</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>以 operational period 管理目標、任務、IAP 與報告。</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>GP2, GP5</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>指揮官、計畫組、幕僚</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>可建立作業週期、設定目標、關聯事件/資源/AAR。</t>
         </is>
       </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="K25" s="14" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>NIMS/ICS workflow；RBAC；IAP data model。</t>
         </is>
       </c>
-      <c r="L25" s="14" t="inlineStr">
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>NIMS / ICS Planning P</t>
         </is>
       </c>
-      <c r="M25" s="14" t="inlineStr">
+      <c r="M25" s="22" t="inlineStr">
         <is>
           <t>Medium–High</t>
         </is>
       </c>
-      <c r="N25" s="14" t="inlineStr">
+      <c r="N25" s="22" t="inlineStr">
         <is>
           <t>schema、UI、IAP 匯出測試</t>
         </is>
       </c>
-      <c r="O25" s="14" t="inlineStr">
+      <c r="O25" s="22" t="inlineStr">
         <is>
           <t>後續支援 ICS operational period</t>
         </is>
       </c>
-      <c r="P25" s="14" t="inlineStr">
+      <c r="P25" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q25" s="14" t="inlineStr">
+      <c r="Q25" s="22" t="inlineStr">
         <is>
           <t>排入 v3 或 GovOps workflow</t>
         </is>
       </c>
-      <c r="R25" s="14" t="inlineStr">
+      <c r="R25" s="22" t="inlineStr">
         <is>
           <t>Product / Compliance</t>
         </is>
       </c>
-      <c r="S25" s="14" t="inlineStr">
+      <c r="S25" s="22" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="T25" s="14" t="inlineStr">
+      <c r="T25" s="22" t="inlineStr">
         <is>
           <t>Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="70" customHeight="1" s="6">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="26" ht="70" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>CAP-022</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>ICS Forms Export</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>ICS / Reporting</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>輸出 ICS 214、201、209、213RR 等表單或相容報表。</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>GP1, GP2, GP4</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>演訓顧問、客戶承辦、標案</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I26" s="14" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>至少 ICS 214 完整；GovOps 需 201/209/213RR 等資料基礎。</t>
         </is>
       </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="K26" s="14" t="inlineStr">
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>資料欄位完整性；不可過度宣稱 FEMA compliant。</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="L26" s="22" t="inlineStr">
         <is>
           <t>FEMA ICS Forms / ICS 508</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr">
+      <c r="M26" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N26" s="14" t="inlineStr">
+      <c r="N26" s="22" t="inlineStr">
         <is>
           <t>表單匯出、欄位 mapping、樣本報告</t>
         </is>
       </c>
-      <c r="O26" s="14" t="inlineStr">
+      <c r="O26" s="22" t="inlineStr">
         <is>
           <t>部分對應 FEMA ICS 表單資料需求</t>
         </is>
       </c>
-      <c r="P26" s="14" t="inlineStr">
+      <c r="P26" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q26" s="14" t="inlineStr">
+      <c r="Q26" s="22" t="inlineStr">
         <is>
           <t>建立 ICS forms coverage matrix 與匯出優先序</t>
         </is>
       </c>
-      <c r="R26" s="14" t="inlineStr">
+      <c r="R26" s="22" t="inlineStr">
         <is>
           <t>Compliance / Reporting</t>
         </is>
       </c>
-      <c r="S26" s="14" t="inlineStr">
+      <c r="S26" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="T26" s="14" t="inlineStr">
+      <c r="T26" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="70" customHeight="1" s="6">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="27" ht="70" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>CAP-023</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>Backup / Restore</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>Ops / Reliability</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>SQLite online backup、壓縮、驗證、還原演練與異地保存。</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>GP4, GP5</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>DevOps、客戶 IT</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>可備份、verify、還原預演；L3 需 DR drill report。</t>
         </is>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="J27" s="22" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
+      <c r="K27" s="22" t="inlineStr">
         <is>
           <t>C3-D；DR playbook；retention。</t>
         </is>
       </c>
-      <c r="L27" s="14" t="inlineStr">
+      <c r="L27" s="22" t="inlineStr">
         <is>
           <t>NIST CP / Recover</t>
         </is>
       </c>
-      <c r="M27" s="14" t="inlineStr">
+      <c r="M27" s="22" t="inlineStr">
         <is>
           <t>High：備份可能含個資</t>
         </is>
       </c>
-      <c r="N27" s="14" t="inlineStr">
+      <c r="N27" s="22" t="inlineStr">
         <is>
           <t>backup log、restore test、DR drill report</t>
         </is>
       </c>
-      <c r="O27" s="14" t="inlineStr">
+      <c r="O27" s="22" t="inlineStr">
         <is>
           <t>支援備份與還原機制</t>
         </is>
       </c>
-      <c r="P27" s="14" t="inlineStr">
+      <c r="P27" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q27" s="14" t="inlineStr">
+      <c r="Q27" s="22" t="inlineStr">
         <is>
           <t>補 systemd/timer、DR playbook、演練紀錄</t>
         </is>
       </c>
-      <c r="R27" s="14" t="inlineStr">
+      <c r="R27" s="22" t="inlineStr">
         <is>
           <t>DevOps / Backend</t>
         </is>
       </c>
-      <c r="S27" s="14" t="inlineStr">
+      <c r="S27" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T27" s="14" t="inlineStr">
+      <c r="T27" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="70" customHeight="1" s="6">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="28" ht="70" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>CAP-024</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>Deployment / Health Check</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Ops / Deployment</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>部署拓撲、健康檢查、metrics、憑證、服務啟停與維運手冊。</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>GP4</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>DevOps、客戶 IT、資安</t>
         </is>
       </c>
-      <c r="G28" s="14" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I28" s="14" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>新工程師可照文件部署；health/metrics 可監控；prod 強制 TLS。</t>
         </is>
       </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="K28" s="14" t="inlineStr">
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>C3；STRICT_TLS；nginx/step-ca；systemd。</t>
         </is>
       </c>
-      <c r="L28" s="14" t="inlineStr">
+      <c r="L28" s="22" t="inlineStr">
         <is>
           <t>NIST CM / SC / Operations</t>
         </is>
       </c>
-      <c r="M28" s="14" t="inlineStr">
+      <c r="M28" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N28" s="14" t="inlineStr">
+      <c r="N28" s="22" t="inlineStr">
         <is>
           <t>部署 runbook、health output、TLS 驗證</t>
         </is>
       </c>
-      <c r="O28" s="14" t="inlineStr">
+      <c r="O28" s="22" t="inlineStr">
         <is>
           <t>支援可維運部署</t>
         </is>
       </c>
-      <c r="P28" s="14" t="inlineStr">
+      <c r="P28" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q28" s="14" t="inlineStr">
+      <c r="Q28" s="22" t="inlineStr">
         <is>
           <t>補 deployment architecture 與 runbook</t>
         </is>
       </c>
-      <c r="R28" s="14" t="inlineStr">
+      <c r="R28" s="22" t="inlineStr">
         <is>
           <t>DevOps</t>
         </is>
       </c>
-      <c r="S28" s="14" t="inlineStr">
+      <c r="S28" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T28" s="14" t="inlineStr">
+      <c r="T28" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="70" customHeight="1" s="6">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="29" ht="70" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>CAP-025</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>Product Edition Gate</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>Product / Commercial</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>Demo、Exercise Pro、GovOps、Tactical 的功能、合規、宣稱與安全邊界。</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>GP4</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>PM、業務、法務</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>每版功能/限制/最低安全控制/可宣稱用語清楚；授權 gate 可驗證。</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>全部</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>License signature；claim guide；acceptance matrix。</t>
         </is>
       </c>
-      <c r="L29" s="14" t="inlineStr">
+      <c r="L29" s="22" t="inlineStr">
         <is>
           <t>Procurement / Sales governance</t>
         </is>
       </c>
-      <c r="M29" s="14" t="inlineStr">
+      <c r="M29" s="22" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="N29" s="14" t="inlineStr">
+      <c r="N29" s="22" t="inlineStr">
         <is>
           <t>edition matrix、license tests、claim guide</t>
         </is>
       </c>
-      <c r="O29" s="14" t="inlineStr">
+      <c r="O29" s="22" t="inlineStr">
         <is>
           <t>支援分層產品交付</t>
         </is>
       </c>
-      <c r="P29" s="14" t="inlineStr">
+      <c r="P29" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q29" s="14" t="inlineStr">
+      <c r="Q29" s="22" t="inlineStr">
         <is>
           <t>建立 edition_feature_matrix 與 license gate</t>
         </is>
       </c>
-      <c r="R29" s="14" t="inlineStr">
+      <c r="R29" s="22" t="inlineStr">
         <is>
           <t>PM / Legal / Product</t>
         </is>
       </c>
-      <c r="S29" s="14" t="inlineStr">
+      <c r="S29" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="T29" s="14" t="inlineStr">
+      <c r="T29" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="70" customHeight="1" s="6">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="30" ht="70" customHeight="1">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>CAP-026</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Claim Language Guardrail</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>Product / Compliance</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>定義可以說、謹慎說、不可說的合規與功能宣稱。</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>GP4</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>業務、法務、PM</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I30" s="14" t="inlineStr">
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>所有 sales copy 與標案文字遵守 claim guide；避免 NIST/FEMA 過度宣稱。</t>
         </is>
       </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="J30" s="22" t="inlineStr">
         <is>
           <t>全部</t>
         </is>
       </c>
-      <c r="K30" s="14" t="inlineStr">
+      <c r="K30" s="22" t="inlineStr">
         <is>
           <t>需結合實際 evidence 與 profile。</t>
         </is>
       </c>
-      <c r="L30" s="14" t="inlineStr">
+      <c r="L30" s="22" t="inlineStr">
         <is>
           <t>Procurement / Legal</t>
         </is>
       </c>
-      <c r="M30" s="14" t="inlineStr">
+      <c r="M30" s="22" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="N30" s="14" t="inlineStr">
+      <c r="N30" s="22" t="inlineStr">
         <is>
           <t>claim guide、審查紀錄</t>
         </is>
       </c>
-      <c r="O30" s="14" t="inlineStr">
+      <c r="O30" s="22" t="inlineStr">
         <is>
           <t>參考/對齊，而非 certified</t>
         </is>
       </c>
-      <c r="P30" s="14" t="inlineStr">
+      <c r="P30" s="22" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="Q30" s="14" t="inlineStr">
+      <c r="Q30" s="22" t="inlineStr">
         <is>
           <t>將 claim guide 納入 release/標案審查</t>
         </is>
       </c>
-      <c r="R30" s="14" t="inlineStr">
+      <c r="R30" s="22" t="inlineStr">
         <is>
           <t>Legal / PM</t>
         </is>
       </c>
-      <c r="S30" s="14" t="inlineStr">
+      <c r="S30" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="T30" s="14" t="inlineStr">
+      <c r="T30" s="22" t="inlineStr">
         <is>
           <t>Internal Only</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="70" customHeight="1" s="6">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="31" ht="70" customHeight="1">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>CAP-027</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>Data Classification / Retention</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>Data Governance</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>資料分類、保存期限、匯出限制、清除、去識別化與訓練用途。</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>GP3, GP4, GP5</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>PM、法務、資安、客戶</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I31" s="14" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>每類資料有敏感度、保存期、匯出、加密、AAR/AI 使用規則。</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>GovOps / Tactical</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr">
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>PII policy；training data consent；retention。</t>
         </is>
       </c>
-      <c r="L31" s="14" t="inlineStr">
+      <c r="L31" s="22" t="inlineStr">
         <is>
           <t>個資法 / NIST PT / Privacy</t>
         </is>
       </c>
-      <c r="M31" s="14" t="inlineStr">
+      <c r="M31" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N31" s="14" t="inlineStr">
+      <c r="N31" s="22" t="inlineStr">
         <is>
           <t>資料分類表、保存政策、清除紀錄</t>
         </is>
       </c>
-      <c r="O31" s="14" t="inlineStr">
+      <c r="O31" s="22" t="inlineStr">
         <is>
           <t>支援資料治理與保存策略</t>
         </is>
       </c>
-      <c r="P31" s="14" t="inlineStr">
+      <c r="P31" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q31" s="14" t="inlineStr">
+      <c r="Q31" s="22" t="inlineStr">
         <is>
           <t>建立 data classification &amp; retention matrix</t>
         </is>
       </c>
-      <c r="R31" s="14" t="inlineStr">
+      <c r="R31" s="22" t="inlineStr">
         <is>
           <t>Data / Legal / Security</t>
         </is>
       </c>
-      <c r="S31" s="14" t="inlineStr">
+      <c r="S31" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T31" s="14" t="inlineStr">
+      <c r="T31" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="70" customHeight="1" s="6">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="32" ht="70" customHeight="1">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>CAP-028</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>AI Summary / Classification</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>AI</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>AI 將文字/語音紀錄整理、分類與摘要，供人工確認。</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>GP1, GP2</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>幕僚、AAR 分析者</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I32" s="14" t="inlineStr">
+      <c r="I32" s="22" t="inlineStr">
         <is>
           <t>AI 只產生草稿；必須標示來源與信心；人工批准後才入報告。</t>
         </is>
       </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="J32" s="22" t="inlineStr">
         <is>
           <t>Flagship / GovOps optional</t>
         </is>
       </c>
-      <c r="K32" s="14" t="inlineStr">
+      <c r="K32" s="22" t="inlineStr">
         <is>
           <t>AI governance；PII redaction；human-in-the-loop。</t>
         </is>
       </c>
-      <c r="L32" s="14" t="inlineStr">
+      <c r="L32" s="22" t="inlineStr">
         <is>
           <t>AI governance / Privacy</t>
         </is>
       </c>
-      <c r="M32" s="14" t="inlineStr">
+      <c r="M32" s="22" t="inlineStr">
         <is>
           <t>Medium–High</t>
         </is>
       </c>
-      <c r="N32" s="14" t="inlineStr">
+      <c r="N32" s="22" t="inlineStr">
         <is>
           <t>AI output log、source attribution、approval record</t>
         </is>
       </c>
-      <c r="O32" s="14" t="inlineStr">
+      <c r="O32" s="22" t="inlineStr">
         <is>
           <t>AI 輔助整理，不取代指揮決策</t>
         </is>
       </c>
-      <c r="P32" s="14" t="inlineStr">
+      <c r="P32" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q32" s="14" t="inlineStr">
+      <c r="Q32" s="22" t="inlineStr">
         <is>
           <t>先做 AI capability ladder，從 AAR 草稿開始</t>
         </is>
       </c>
-      <c r="R32" s="14" t="inlineStr">
+      <c r="R32" s="22" t="inlineStr">
         <is>
           <t>AI / Product</t>
         </is>
       </c>
-      <c r="S32" s="14" t="inlineStr">
+      <c r="S32" s="22" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="T32" s="14" t="inlineStr">
+      <c r="T32" s="22" t="inlineStr">
         <is>
           <t>Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="70" customHeight="1" s="6">
-      <c r="A33" s="14" t="inlineStr">
+    <row r="33" ht="70" customHeight="1">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>CAP-029</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>AI AAR Draft</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>AI / AAR</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>根據 timeline、事件、決策、回報產生 AAR 草稿。</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>GP1</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>AAR 分析者、演訓顧問</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>草稿可追溯來源；人工審核；不得自動輸出正式結論。</t>
         </is>
       </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="J33" s="22" t="inlineStr">
         <is>
           <t>Flagship / Exercise Pro optional</t>
         </is>
       </c>
-      <c r="K33" s="14" t="inlineStr">
+      <c r="K33" s="22" t="inlineStr">
         <is>
           <t>AI governance；AAR reproducibility。</t>
         </is>
       </c>
-      <c r="L33" s="14" t="inlineStr">
+      <c r="L33" s="22" t="inlineStr">
         <is>
           <t>HSEEP AAR-IP / AI governance</t>
         </is>
       </c>
-      <c r="M33" s="14" t="inlineStr">
+      <c r="M33" s="22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N33" s="14" t="inlineStr">
+      <c r="N33" s="22" t="inlineStr">
         <is>
           <t>草稿樣本、來源引用、審核紀錄</t>
         </is>
       </c>
-      <c r="O33" s="14" t="inlineStr">
+      <c r="O33" s="22" t="inlineStr">
         <is>
           <t>AI 輔助 AAR 草稿生成</t>
         </is>
       </c>
-      <c r="P33" s="14" t="inlineStr">
+      <c r="P33" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q33" s="14" t="inlineStr">
+      <c r="Q33" s="22" t="inlineStr">
         <is>
           <t>建立 AAR source map 後再導入 AI</t>
         </is>
       </c>
-      <c r="R33" s="14" t="inlineStr">
+      <c r="R33" s="22" t="inlineStr">
         <is>
           <t>AI / AAR</t>
         </is>
       </c>
-      <c r="S33" s="14" t="inlineStr">
+      <c r="S33" s="22" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="T33" s="14" t="inlineStr">
+      <c r="T33" s="22" t="inlineStr">
         <is>
           <t>Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="70" customHeight="1" s="6">
-      <c r="A34" s="14" t="inlineStr">
+    <row r="34" ht="70" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>CAP-030</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>Silent Scribe</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>Tactical / AI</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>戰術版語音/現場紀錄工具，以 ICS_DMAS 為後端，但屬獨立產品線。</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="22" t="inlineStr">
         <is>
           <t>GP2, GP5</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>前線人員、民防/準軍事組織</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I34" s="14" t="inlineStr">
+      <c r="I34" s="22" t="inlineStr">
         <is>
           <t>語音轉事件草稿；不可直接下決策；資料可加密與安全清除。</t>
         </is>
       </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="J34" s="22" t="inlineStr">
         <is>
           <t>Tactical</t>
         </is>
       </c>
-      <c r="K34" s="14" t="inlineStr">
+      <c r="K34" s="22" t="inlineStr">
         <is>
           <t>mTLS/WireGuard；Panic Wipe；PII/tactical data governance。</t>
         </is>
       </c>
-      <c r="L34" s="14" t="inlineStr">
+      <c r="L34" s="22" t="inlineStr">
         <is>
           <t>High-sensitivity field operations</t>
         </is>
       </c>
-      <c r="M34" s="14" t="inlineStr">
+      <c r="M34" s="22" t="inlineStr">
         <is>
           <t>Critical：戰術/位置/語音</t>
         </is>
       </c>
-      <c r="N34" s="14" t="inlineStr">
+      <c r="N34" s="22" t="inlineStr">
         <is>
           <t>安全設計、裝置測試、資料銷毀紀錄</t>
         </is>
       </c>
-      <c r="O34" s="14" t="inlineStr">
+      <c r="O34" s="22" t="inlineStr">
         <is>
           <t>高敏感版本需獨立驗收</t>
         </is>
       </c>
-      <c r="P34" s="14" t="inlineStr">
+      <c r="P34" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q34" s="14" t="inlineStr">
+      <c r="Q34" s="22" t="inlineStr">
         <is>
           <t>保持與 GovOps 分線，不併入基礎產品</t>
         </is>
       </c>
-      <c r="R34" s="14" t="inlineStr">
+      <c r="R34" s="22" t="inlineStr">
         <is>
           <t>Tactical / AI / Security</t>
         </is>
       </c>
-      <c r="S34" s="14" t="inlineStr">
+      <c r="S34" s="22" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="T34" s="14" t="inlineStr">
+      <c r="T34" s="22" t="inlineStr">
         <is>
           <t>Partner Restricted</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="70" customHeight="1" s="6">
-      <c r="A35" s="14" t="inlineStr">
+    <row r="35" ht="70" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>CAP-031</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>Incident Response Playbook</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>Ops / Security</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>資安事件、資料污染、Pi 被奪、個資外洩、同步異常的處置流程。</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>GP5</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>資安、DevOps、客戶 IT</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>有分類、通報、隔離、復原、證據保存與桌上演練紀錄。</t>
         </is>
       </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="J35" s="22" t="inlineStr">
         <is>
           <t>GovOps / Tactical</t>
         </is>
       </c>
-      <c r="K35" s="14" t="inlineStr">
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>C1/C3；IR/DR；audit evidence。</t>
         </is>
       </c>
-      <c r="L35" s="14" t="inlineStr">
+      <c r="L35" s="22" t="inlineStr">
         <is>
           <t>NIST 800-61 / CSF Respond</t>
         </is>
       </c>
-      <c r="M35" s="14" t="inlineStr">
+      <c r="M35" s="22" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N35" s="14" t="inlineStr">
+      <c r="N35" s="22" t="inlineStr">
         <is>
           <t>IR playbook、演練紀錄、post-incident template</t>
         </is>
       </c>
-      <c r="O35" s="14" t="inlineStr">
+      <c r="O35" s="22" t="inlineStr">
         <is>
           <t>支援事件應變流程</t>
         </is>
       </c>
-      <c r="P35" s="14" t="inlineStr">
+      <c r="P35" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q35" s="14" t="inlineStr">
+      <c r="Q35" s="22" t="inlineStr">
         <is>
           <t>先針對資料污染與 Pi compromise 建立 playbook</t>
         </is>
       </c>
-      <c r="R35" s="14" t="inlineStr">
+      <c r="R35" s="22" t="inlineStr">
         <is>
           <t>Security / Ops</t>
         </is>
       </c>
-      <c r="S35" s="14" t="inlineStr">
+      <c r="S35" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="T35" s="14" t="inlineStr">
+      <c r="T35" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="70" customHeight="1" s="6">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="36" ht="70" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>CAP-032</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>Accessibility / WCAG</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>Quality / Accessibility</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>三端 PWA 與儀表板達到基本無障礙與現場可用性。</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="22" t="inlineStr">
         <is>
           <t>GP4</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>QA、PM、客戶驗收</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G36" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="I36" s="22" t="inlineStr">
         <is>
           <t>WCAG AA 測試；關鍵操作可鍵盤/讀屏；字體與對比符合。</t>
         </is>
       </c>
-      <c r="J36" s="14" t="inlineStr">
+      <c r="J36" s="22" t="inlineStr">
         <is>
           <t>GovOps / C6</t>
         </is>
       </c>
-      <c r="K36" s="14" t="inlineStr">
+      <c r="K36" s="22" t="inlineStr">
         <is>
           <t>C6；accessibility test plan。</t>
         </is>
       </c>
-      <c r="L36" s="14" t="inlineStr">
+      <c r="L36" s="22" t="inlineStr">
         <is>
           <t>WCAG 2.0 AA / Procurement</t>
         </is>
       </c>
-      <c r="M36" s="14" t="inlineStr">
+      <c r="M36" s="22" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="N36" s="14" t="inlineStr">
+      <c r="N36" s="22" t="inlineStr">
         <is>
           <t>WCAG report、Lighthouse、manual tests</t>
         </is>
       </c>
-      <c r="O36" s="14" t="inlineStr">
+      <c r="O36" s="22" t="inlineStr">
         <is>
           <t>支援無障礙驗收（完成後）</t>
         </is>
       </c>
-      <c r="P36" s="14" t="inlineStr">
+      <c r="P36" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q36" s="14" t="inlineStr">
+      <c r="Q36" s="22" t="inlineStr">
         <is>
           <t>建立 accessibility test plan</t>
         </is>
       </c>
-      <c r="R36" s="14" t="inlineStr">
+      <c r="R36" s="22" t="inlineStr">
         <is>
           <t>QA / Frontend</t>
         </is>
       </c>
-      <c r="S36" s="14" t="inlineStr">
+      <c r="S36" s="22" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="T36" s="14" t="inlineStr">
+      <c r="T36" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="70" customHeight="1" s="6">
-      <c r="A37" s="14" t="inlineStr">
+    <row r="37" ht="70" customHeight="1">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>CAP-033</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>Field Usability</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>UX / Field</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>災害現場壓力、低光、平板、戴手套、志工操作下的可用性。</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>GP2, GP3</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>PM、UX、演訓顧問、現場操作員</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H37" s="14" t="inlineStr">
+      <c r="H37" s="22" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="I37" s="22" t="inlineStr">
         <is>
           <t>關鍵填報流程少步驟；離線/同步狀態清楚；錯誤可回復。</t>
         </is>
       </c>
-      <c r="J37" s="14" t="inlineStr">
+      <c r="J37" s="22" t="inlineStr">
         <is>
           <t>Exercise Pro / Tactical</t>
         </is>
       </c>
-      <c r="K37" s="14" t="inlineStr">
+      <c r="K37" s="22" t="inlineStr">
         <is>
           <t>不直接是資安，但影響資料品質與採用率。</t>
         </is>
       </c>
-      <c r="L37" s="14" t="inlineStr">
+      <c r="L37" s="22" t="inlineStr">
         <is>
           <t>Operational usability</t>
         </is>
       </c>
-      <c r="M37" s="14" t="inlineStr">
+      <c r="M37" s="22" t="inlineStr">
         <is>
           <t>Medium：可能造成錯誤資料</t>
         </is>
       </c>
-      <c r="N37" s="14" t="inlineStr">
+      <c r="N37" s="22" t="inlineStr">
         <is>
           <t>field test checklist、觀察紀錄、UX issue list</t>
         </is>
       </c>
-      <c r="O37" s="14" t="inlineStr">
+      <c r="O37" s="22" t="inlineStr">
         <is>
           <t>支援現場操作友善性</t>
         </is>
       </c>
-      <c r="P37" s="14" t="inlineStr">
+      <c r="P37" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q37" s="14" t="inlineStr">
+      <c r="Q37" s="22" t="inlineStr">
         <is>
           <t>安排 tabletop + field usability test</t>
         </is>
       </c>
-      <c r="R37" s="14" t="inlineStr">
+      <c r="R37" s="22" t="inlineStr">
         <is>
           <t>UX / Product</t>
         </is>
       </c>
-      <c r="S37" s="14" t="inlineStr">
+      <c r="S37" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="T37" s="14" t="inlineStr">
+      <c r="T37" s="22" t="inlineStr">
         <is>
           <t>Customer Summary</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="70" customHeight="1" s="6">
-      <c r="A38" s="14" t="inlineStr">
+    <row r="38" ht="70" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>CAP-034</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>Release Evidence Pack</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>Release / Procurement</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>每版 release 的測試、SBOM、弱掃、備份驗證、合規對照與已知限制。</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>GP4</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>PM、DevOps、標案、客戶資安</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G38" s="22" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H38" s="22" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr">
+      <c r="I38" s="22" t="inlineStr">
         <is>
           <t>每版有 coverage、SAST/SCA、SBOM、known issues、backup verify、acceptance matrix。</t>
         </is>
       </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="J38" s="22" t="inlineStr">
         <is>
           <t>GovOps / C6</t>
         </is>
       </c>
-      <c r="K38" s="14" t="inlineStr">
+      <c r="K38" s="22" t="inlineStr">
         <is>
           <t>C2/C6；no high/critical for release gate。</t>
         </is>
       </c>
-      <c r="L38" s="14" t="inlineStr">
+      <c r="L38" s="22" t="inlineStr">
         <is>
           <t>NIST SSDF / Supply Chain</t>
         </is>
       </c>
-      <c r="M38" s="14" t="inlineStr">
+      <c r="M38" s="22" t="inlineStr">
         <is>
           <t>Low–High：視附錄</t>
         </is>
       </c>
-      <c r="N38" s="14" t="inlineStr">
+      <c r="N38" s="22" t="inlineStr">
         <is>
           <t>release evidence pack、SBOM、scan report</t>
         </is>
       </c>
-      <c r="O38" s="14" t="inlineStr">
+      <c r="O38" s="22" t="inlineStr">
         <is>
           <t>可提供交付證據包</t>
         </is>
       </c>
-      <c r="P38" s="14" t="inlineStr">
+      <c r="P38" s="22" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="Q38" s="14" t="inlineStr">
+      <c r="Q38" s="22" t="inlineStr">
         <is>
           <t>建立 evidence_pack_template 與 CI artifacts</t>
         </is>
       </c>
-      <c r="R38" s="14" t="inlineStr">
+      <c r="R38" s="22" t="inlineStr">
         <is>
           <t>Release / DevOps</t>
         </is>
       </c>
-      <c r="S38" s="14" t="inlineStr">
+      <c r="S38" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="T38" s="14" t="inlineStr">
+      <c r="T38" s="22" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CAP-035</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Commander Frontend Security</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Security / Auth</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>commander_dashboard.html 模組化：移除 inline JS，CSP enforce，為 RBAC UI 提供安全基礎。</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>GP2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Frontend / Security</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>L0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>移除所有 inline script/handler；CSP enforce 不含 unsafe-inline；vitest + pytest green。</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Exercise Pro</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>C1-F; 阻擋 RBAC P0 (CAP-014)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NIST SC-18, AC-3, V14.4(3)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>PR# (TBD); AC-1~AC-14 all green</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>支援 commander 路徑 XSS 防護</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>C1-F close after frontend+CSP task</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Frontend / Security</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Internal Only</t>
         </is>
       </c>
     </row>
@@ -4875,183 +5902,178 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="12" customWidth="1" style="6" min="1" max="1"/>
-    <col width="34" customWidth="1" style="6" min="2" max="2"/>
-    <col width="78" customWidth="1" style="6" min="3" max="3"/>
-    <col width="28" customWidth="1" style="6" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="6">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Golden Paths</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="17" t="n"/>
-      <c r="F1" s="17" t="n"/>
-      <c r="G1" s="17" t="n"/>
-      <c r="H1" s="17" t="n"/>
-      <c r="I1" s="17" t="n"/>
-      <c r="J1" s="17" t="n"/>
-      <c r="K1" s="17" t="n"/>
-      <c r="L1" s="17" t="n"/>
-      <c r="M1" s="17" t="n"/>
-      <c r="N1" s="17" t="n"/>
-      <c r="O1" s="17" t="n"/>
-      <c r="P1" s="17" t="n"/>
-      <c r="Q1" s="17" t="n"/>
-      <c r="R1" s="17" t="n"/>
-      <c r="S1" s="17" t="n"/>
-      <c r="T1" s="17" t="n"/>
-      <c r="U1" s="17" t="n"/>
-      <c r="V1" s="17" t="n"/>
-      <c r="W1" s="17" t="n"/>
-      <c r="X1" s="17" t="n"/>
-      <c r="Y1" s="17" t="n"/>
-      <c r="Z1" s="17" t="n"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" s="6">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="4" t="n"/>
+      <c r="Y1" s="4" t="n"/>
+      <c r="Z1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>端到端產品主線，用來確認 capability 是否真的串成可演示、可演訓、可驗收的工作流。</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-    </row>
-    <row r="4" ht="34" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
+    </row>
+    <row r="3"/>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>GP ID</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Golden Path</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Primary Use</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1" s="6">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>GP1</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>TTX → 決策 → AAR</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>演訓建立、狀況注入、受訓單位回應、指揮決策、事件時間線、AAR 與改善事項。</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>C5 land-and-expand / Exercise Pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1" s="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>v3.0.0 GovOps+TTX (NOT Exercise Pro — GP1 requires MSEL inject + AAR engine)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>GP2</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>現場回報 → COP → 任務/決策 → 回報</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>收容、醫療、前進組或 Field Node 回報進入 COP，指揮部決策並追蹤任務回報。</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1" s="6">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>GP3</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>斷網 → 離線資料 → 恢復同步 → AAR 可追溯</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>PWA / Pi / QR 在斷網下暫存與恢復同步，衝突處理後保留來源、時間差與採納狀態。</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps / Tactical</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1" s="6">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>GP4</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>部署 → 驗收 → 證據包</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>客戶部署、健康檢查、備份還原、測試報告、SBOM、弱掃與驗收文件交付。</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>GovOps / C6</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1" s="6">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>GP5</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>真實災害輔助 → IR/DR → 稽核保存</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>支援高敏感資料、事件應變、復原演練、不可竄改紀錄與長期稽核保存。</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>GovOps / Tactical / C6</t>
         </is>
@@ -5076,183 +6098,177 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="10" customWidth="1" style="6" min="1" max="1"/>
-    <col width="22" customWidth="1" style="6" min="2" max="2"/>
-    <col width="78" customWidth="1" style="6" min="3" max="3"/>
-    <col width="50" customWidth="1" style="6" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="6">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Maturity Definitions</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="17" t="n"/>
-      <c r="F1" s="17" t="n"/>
-      <c r="G1" s="17" t="n"/>
-      <c r="H1" s="17" t="n"/>
-      <c r="I1" s="17" t="n"/>
-      <c r="J1" s="17" t="n"/>
-      <c r="K1" s="17" t="n"/>
-      <c r="L1" s="17" t="n"/>
-      <c r="M1" s="17" t="n"/>
-      <c r="N1" s="17" t="n"/>
-      <c r="O1" s="17" t="n"/>
-      <c r="P1" s="17" t="n"/>
-      <c r="Q1" s="17" t="n"/>
-      <c r="R1" s="17" t="n"/>
-      <c r="S1" s="17" t="n"/>
-      <c r="T1" s="17" t="n"/>
-      <c r="U1" s="17" t="n"/>
-      <c r="V1" s="17" t="n"/>
-      <c r="W1" s="17" t="n"/>
-      <c r="X1" s="17" t="n"/>
-      <c r="Y1" s="17" t="n"/>
-      <c r="Z1" s="17" t="n"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" s="6">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="4" t="n"/>
+      <c r="Y1" s="4" t="n"/>
+      <c r="Z1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>用 L0–L4 區分『有功能』與『可交付、可稽核、可支援高敏感場景』。</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-    </row>
-    <row r="4" ht="34" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Claim Boundary</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1" s="6">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>L0</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Not Implemented</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>尚未實作，僅存在於 roadmap / backlog。</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>不可對外宣稱。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1" s="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Demo</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>可演示或 PoC，但不能依賴於正式演訓或真實場景。</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>可在受控 demo 使用，須標示限制。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1" s="6">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Operational</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>可在受控正式演訓中穩定使用，有基本錯誤處理與操作流程。</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>可作為 Exercise Pro 驗收項。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1" s="6">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Auditable</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>具備權限、稽核、證據、測試與可追溯性，可支援採購驗收。</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>可作為 GovOps / 標案驗收項。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1" s="6">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>L4</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Mission-ready</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>可支援真實災害輔助或高敏感場景，含 IR/DR、加密、外部稽核與操作訓練。</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>僅 Tactical / 高階 GovOps 可主張。</t>
         </is>
@@ -5276,164 +6292,269 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Z16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="24" customWidth="1" style="6" min="1" max="1"/>
-    <col width="38" customWidth="1" style="6" min="2" max="2"/>
-    <col width="78" customWidth="1" style="6" min="3" max="3"/>
-    <col width="34" customWidth="1" style="6" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="6">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Edition Gates</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="17" t="n"/>
-      <c r="F1" s="17" t="n"/>
-      <c r="G1" s="17" t="n"/>
-      <c r="H1" s="17" t="n"/>
-      <c r="I1" s="17" t="n"/>
-      <c r="J1" s="17" t="n"/>
-      <c r="K1" s="17" t="n"/>
-      <c r="L1" s="17" t="n"/>
-      <c r="M1" s="17" t="n"/>
-      <c r="N1" s="17" t="n"/>
-      <c r="O1" s="17" t="n"/>
-      <c r="P1" s="17" t="n"/>
-      <c r="Q1" s="17" t="n"/>
-      <c r="R1" s="17" t="n"/>
-      <c r="S1" s="17" t="n"/>
-      <c r="T1" s="17" t="n"/>
-      <c r="U1" s="17" t="n"/>
-      <c r="V1" s="17" t="n"/>
-      <c r="W1" s="17" t="n"/>
-      <c r="X1" s="17" t="n"/>
-      <c r="Y1" s="17" t="n"/>
-      <c r="Z1" s="17" t="n"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" s="6">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="4" t="n"/>
+      <c r="Y1" s="4" t="n"/>
+      <c r="Z1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>把 capability 綁到產品版本、可宣稱用途與最低安全/合規條件。</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-    </row>
-    <row r="4" ht="34" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
+    </row>
+    <row r="3"/>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Edition</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Use Case</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Minimum Conditions</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Disclosure / Deliverable Level</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1" s="6">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Demo / Community</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>受控展示、假資料、低敏感資料</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>不處理真實個資；安全 baseline 需修掉 current-stage P0。</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Public / Sales Safe</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1" s="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Exercise Pro</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>正式演訓、TTX、AAR、基本資安</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>需完成 Trusted Ingest、基本 RBAC、AAR 可追溯初版、備份還原。</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>現場演練（field drill）、基本資安</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>需完成 Trusted Ingest (#11)、基本 RBAC (CAP-014)、CSP enforce (CAP-035)、備份還原 (CAP-023)。
+不支援 TTX MSEL inject 或自動 AAR report（見 GovOps+TTX）。</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Customer Deliverable</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1" s="6">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>政府採購、個資、audit、DR、正式驗收</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>需 C1/C2/C3 證據包、PII 控制、audit evidence、IR/DR、SBOM。</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Customer Deliverable / Procurement</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1" s="6">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Tactical</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Field Node、戰術敏感、高安全部署</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>需裝置憑證、mTLS/WireGuard、Panic Wipe、LUKS、戰術資料治理。</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Partner Restricted</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Priority → Edition Mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Blocks Edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>Current stage must-fix; minimum prerequisite for any external claim</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>ALL Editions</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>Must complete before Exercise Pro / GovOps</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Exercise Pro and above</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>GovOps procurement hardening</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>GovOps and above</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>Moat / full compliance</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Flagship</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="inlineStr">
+        <is>
+          <t>Tactical high-security scenarios</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="inlineStr">
+        <is>
+          <t>Tactical only</t>
         </is>
       </c>
     </row>
@@ -5456,293 +6577,287 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="30" customWidth="1" style="6" min="1" max="1"/>
-    <col width="82" customWidth="1" style="6" min="2" max="2"/>
-    <col width="28" customWidth="1" style="6" min="3" max="3"/>
-    <col width="26" customWidth="1" style="6" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="6">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Acceptance Evidence</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="17" t="n"/>
-      <c r="F1" s="17" t="n"/>
-      <c r="G1" s="17" t="n"/>
-      <c r="H1" s="17" t="n"/>
-      <c r="I1" s="17" t="n"/>
-      <c r="J1" s="17" t="n"/>
-      <c r="K1" s="17" t="n"/>
-      <c r="L1" s="17" t="n"/>
-      <c r="M1" s="17" t="n"/>
-      <c r="N1" s="17" t="n"/>
-      <c r="O1" s="17" t="n"/>
-      <c r="P1" s="17" t="n"/>
-      <c r="Q1" s="17" t="n"/>
-      <c r="R1" s="17" t="n"/>
-      <c r="S1" s="17" t="n"/>
-      <c r="T1" s="17" t="n"/>
-      <c r="U1" s="17" t="n"/>
-      <c r="V1" s="17" t="n"/>
-      <c r="W1" s="17" t="n"/>
-      <c r="X1" s="17" t="n"/>
-      <c r="Y1" s="17" t="n"/>
-      <c r="Z1" s="17" t="n"/>
-    </row>
-    <row r="2" ht="34" customHeight="1" s="6">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="4" t="n"/>
+      <c r="Y1" s="4" t="n"/>
+      <c r="Z1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>常見 capability 的驗收證據索引；主表 Evidence Required 欄可連回本頁。</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-    </row>
-    <row r="4" ht="34" customHeight="1" s="6">
-      <c r="A4" s="8" t="inlineStr">
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Capability</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Evidence Required</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Edition / Gate</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1" s="6">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TTX Inject</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Inject 簽章測試、送達/閱讀/回應紀錄、TTX/real session 隔離測試</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>TTX / Security</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1" s="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>AAR Timeline</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>AAR 匯出、事件來源連結、audit 對照、回放測試</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>AAR / QA</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1" s="6">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Command COP</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>E2E 資料流測試、dashboard 截圖、資料來源時間標示</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Exercise Pro</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Product / Frontend</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1" s="6">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>PWA Field Report</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>離線填報測試、恢復同步測試、採納/退回流程測試</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Exercise Pro</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>PWA / QA</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1" s="6">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Trusted Ingest</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>無簽章拒收、重放拒收、body tamper 拒收、key rotation 測試</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Security / Backend</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="52" customHeight="1" s="6">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>WebSocket Gate</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>未 auth delta/sync_push 拒收、session_restore 不接受 client 自報 role</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Exercise Pro / GovOps</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Node / Security</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="52" customHeight="1" s="6">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>RBAC</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Endpoint role matrix、API regression tests、session revoke 測試</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="52" customHeight="1" s="6">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Audit Evidence</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Hash chain 驗證、append-only trigger、reset 不刪 audit 測試</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Security / Backend</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1" s="6">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Backup / Restore</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Online backup、checksum verify、restore drill report、retention 記錄</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>GovOps</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>DevOps</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1" s="6">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Release Evidence Pack</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Coverage、SAST/SCA、SBOM、known issues、acceptance matrix</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>GovOps / C6</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Release / PM</t>
         </is>
@@ -5758,4 +6873,417 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>Issue → Capability → GAP Traceability Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Issue#</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Seq</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>CAP affected</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>GAP resolved</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>PR#</t>
+        </is>
+      </c>
+      <c r="H3" s="26" t="inlineStr">
+        <is>
+          <t>Status / Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Pi first-run security</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>B-P0</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>CAP-010 (FieldSync)</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>GAP-AUTH-PI-01</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>v0.13.0+v2.1.0</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>CLOSED 2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>WS pre-auth gate</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>B-P0</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>CAP-013 (WSAuth), CAP-010</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>GAP-AUTH-02, GAP-SYNC-17</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>v2.1.0</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="H5" s="27" t="inlineStr">
+        <is>
+          <t>CLOSED 2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>Trusted Ingest HMAC</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>B-P0</t>
+        </is>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>CAP-012 (TrustedIngest), CAP-010</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>GAP-SYNC-05</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="inlineStr">
+        <is>
+          <t>v2.1.0</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="H6" s="28" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Structured logging + collect_debug.sh</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>A-Deploy</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>CAP-NEW (Logging)</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="inlineStr">
+        <is>
+          <t>GAP-DEPLOY-18c, GAP-AUDIT-10b</t>
+        </is>
+      </c>
+      <c r="F7" s="30" t="inlineStr">
+        <is>
+          <t>v2.1.0</t>
+        </is>
+      </c>
+      <c r="G7" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>/health liveness endpoint</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>A-Deploy</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>CAP-024 (Deployment/Health)</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>GAP-DEPLOY-07c</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>v2.1.0</t>
+        </is>
+      </c>
+      <c r="G8" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Frontend modularise + CSP</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>B-P0</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>CAP-035 (CommanderFrontend)</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>GAP-AUTH-20b, GAP-AUTH-26</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>v2.1.0</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>4-role RBAC + endpoint gate</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>B-P0</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>CAP-014 (RBAC/Endpoint Gate)</t>
+        </is>
+      </c>
+      <c r="E10" s="29" t="inlineStr">
+        <is>
+          <t>GAP-AUTH-01</t>
+        </is>
+      </c>
+      <c r="F10" s="29" t="inlineStr">
+        <is>
+          <t>v2.1.0</t>
+        </is>
+      </c>
+      <c r="G10" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="29" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Release Acceptance (GP2+GP3 E2E)</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>E-Accept</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>All GP2/GP3 CAPs</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>v2.1.0</t>
+        </is>
+      </c>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>PLANNED (last)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/compliance/ICS_DMAS_master_capability_matrix.xlsx
+++ b/docs/compliance/ICS_DMAS_master_capability_matrix.xlsx
@@ -258,7 +258,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -328,6 +328,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2166,7 +2169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z39"/>
+  <dimension ref="A1:Z40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="20"/>
   <cols>
     <col width="21" customWidth="1" style="19" min="1" max="1"/>
@@ -4712,7 +4715,9 @@
       </c>
       <c r="K28" s="22" t="inlineStr">
         <is>
-          <t>C3；STRICT_TLS；nginx/step-ca；systemd。</t>
+          <t>C3-B install script; STRICT_TLS; nginx/step-ca; systemd.
+v2.1.0: /health liveness only (L1 partial — Exercise Pro 序列A).
+v2.2.0: /metrics + Prometheus + alert rules (L2 full — GovOps).</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -4742,7 +4747,8 @@
       </c>
       <c r="Q28" s="22" t="inlineStr">
         <is>
-          <t>補 deployment architecture 與 runbook</t>
+          <t>v2.1.0: implement /health basic liveness ({"status":"ok","version":"x.x.x"}).
+v2.2.0: add /metrics Prometheus + alerting.</t>
         </is>
       </c>
       <c r="R28" s="22" t="inlineStr">
@@ -5878,6 +5884,108 @@
         </is>
       </c>
       <c r="T39" t="inlineStr">
+        <is>
+          <t>Internal Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="38" t="inlineStr">
+        <is>
+          <t>CAP-036</t>
+        </is>
+      </c>
+      <c r="B40" s="38" t="inlineStr">
+        <is>
+          <t>Operational Logging &amp; Debug</t>
+        </is>
+      </c>
+      <c r="C40" s="38" t="inlineStr">
+        <is>
+          <t>Ops / Reliability</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="inlineStr">
+        <is>
+          <t>Structured JSON logging (structlog), correlation ID, 8 priority log positions, log persistence to /var/log/ics/, collect_debug.sh one-command debug package.</t>
+        </is>
+      </c>
+      <c r="E40" s="38" t="inlineStr">
+        <is>
+          <t>GP2, GP3, GP4</t>
+        </is>
+      </c>
+      <c r="F40" s="38" t="inlineStr">
+        <is>
+          <t>DevOps, 現場維運人員</t>
+        </is>
+      </c>
+      <c r="G40" s="38" t="inlineStr">
+        <is>
+          <t>L0</t>
+        </is>
+      </c>
+      <c r="H40" s="38" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="I40" s="38" t="inlineStr">
+        <is>
+          <t>ERROR log 持久化；collect_debug.sh 產出 zip；correlation ID 跨組件追蹤；prod mode 只出 INFO+；8 個優先位置有 log。</t>
+        </is>
+      </c>
+      <c r="J40" s="38" t="inlineStr">
+        <is>
+          <t>Exercise Pro</t>
+        </is>
+      </c>
+      <c r="K40" s="38" t="inlineStr">
+        <is>
+          <t>C1-D; 部署基礎設施，在所有 P0 Security 之前完成</t>
+        </is>
+      </c>
+      <c r="L40" s="38" t="inlineStr">
+        <is>
+          <t>NIST AU-2, AU-3, AU-12, SI-11</t>
+        </is>
+      </c>
+      <c r="M40" s="38" t="inlineStr">
+        <is>
+          <t>Low (log metadata)</t>
+        </is>
+      </c>
+      <c r="N40" s="38" t="inlineStr">
+        <is>
+          <t>PR# (TBD); collect_debug.sh demo; log rotation verify</t>
+        </is>
+      </c>
+      <c r="O40" s="38" t="inlineStr">
+        <is>
+          <t>支援現場問題診斷與事後稽核</t>
+        </is>
+      </c>
+      <c r="P40" s="38" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="Q40" s="38" t="inlineStr">
+        <is>
+          <t>序列 A — 部署基礎設施，最優先</t>
+        </is>
+      </c>
+      <c r="R40" s="38" t="inlineStr">
+        <is>
+          <t>DevOps / Backend</t>
+        </is>
+      </c>
+      <c r="S40" s="38" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="T40" s="38" t="inlineStr">
         <is>
           <t>Internal Only</t>
         </is>
@@ -5946,7 +6054,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -6337,7 +6444,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -7088,7 +7194,7 @@
       </c>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>CAP-NEW (Logging)</t>
+          <t>CAP-036 (Operational Logging)</t>
         </is>
       </c>
       <c r="E7" s="30" t="inlineStr">
@@ -7130,7 +7236,7 @@
       </c>
       <c r="D8" s="30" t="inlineStr">
         <is>
-          <t>CAP-024 (Deployment/Health)</t>
+          <t>CAP-024 (Deployment/Health) — partial L1 (/health only; full L2 in v2.2.0)</t>
         </is>
       </c>
       <c r="E8" s="30" t="inlineStr">
